--- a/data/E-Vocab-Band-II-Core-II.xlsx
+++ b/data/E-Vocab-Band-II-Core-II.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core II Data" sheetId="1" r:id="R15f83e782b22413c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method &amp; Sources" sheetId="2" r:id="R9294b702e1a14a96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core II Data" sheetId="1" r:id="R22a02df332e044b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method &amp; Sources" sheetId="2" r:id="R62b15b66cfd240a6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -639,7 +639,7 @@
         <x:v>1252</x:v>
       </x:c>
       <x:c r="B5" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
         <x:v>Core II</x:v>
@@ -682,7 +682,7 @@
         <x:v>1125</x:v>
       </x:c>
       <x:c r="B6" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
         <x:v>Core II</x:v>
@@ -727,7 +727,7 @@
         <x:v>1405</x:v>
       </x:c>
       <x:c r="B7" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
         <x:v>Core II</x:v>
@@ -778,7 +778,7 @@
         <x:v>1111</x:v>
       </x:c>
       <x:c r="B8" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
         <x:v>Core II</x:v>
@@ -831,7 +831,7 @@
         <x:v>1727</x:v>
       </x:c>
       <x:c r="B9" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
         <x:v>Core II</x:v>
@@ -876,7 +876,7 @@
         <x:v>2037</x:v>
       </x:c>
       <x:c r="B10" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
         <x:v>Core II</x:v>
@@ -919,7 +919,7 @@
         <x:v>1206</x:v>
       </x:c>
       <x:c r="B11" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
         <x:v>Core II</x:v>
@@ -966,7 +966,7 @@
         <x:v>1662</x:v>
       </x:c>
       <x:c r="B12" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1011,7 +1011,7 @@
         <x:v>2176</x:v>
       </x:c>
       <x:c r="B13" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1058,7 +1058,7 @@
         <x:v>1612</x:v>
       </x:c>
       <x:c r="B14" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1103,7 +1103,7 @@
         <x:v>1779</x:v>
       </x:c>
       <x:c r="B15" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1146,7 +1146,7 @@
         <x:v>1857</x:v>
       </x:c>
       <x:c r="B16" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1193,7 +1193,7 @@
         <x:v>2157</x:v>
       </x:c>
       <x:c r="B17" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1236,7 +1236,7 @@
         <x:v>1448</x:v>
       </x:c>
       <x:c r="B18" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1281,7 +1281,7 @@
         <x:v>1311</x:v>
       </x:c>
       <x:c r="B19" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1324,7 +1324,7 @@
         <x:v>1927</x:v>
       </x:c>
       <x:c r="B20" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1367,7 +1367,7 @@
         <x:v>2151</x:v>
       </x:c>
       <x:c r="B21" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1412,7 +1412,7 @@
         <x:v>1434</x:v>
       </x:c>
       <x:c r="B22" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>1320</x:v>
       </x:c>
       <x:c r="B23" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1500,7 +1500,7 @@
         <x:v>2062</x:v>
       </x:c>
       <x:c r="B24" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1543,7 +1543,7 @@
         <x:v>1460</x:v>
       </x:c>
       <x:c r="B25" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1588,7 +1588,7 @@
         <x:v>1965</x:v>
       </x:c>
       <x:c r="B26" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1633,7 +1633,7 @@
         <x:v>2106</x:v>
       </x:c>
       <x:c r="B27" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1676,7 +1676,7 @@
         <x:v>1993</x:v>
       </x:c>
       <x:c r="B28" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1721,7 +1721,7 @@
         <x:v>1624</x:v>
       </x:c>
       <x:c r="B29" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1766,7 +1766,7 @@
         <x:v>1156</x:v>
       </x:c>
       <x:c r="B30" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1809,7 +1809,7 @@
         <x:v>1217</x:v>
       </x:c>
       <x:c r="B31" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1860,7 +1860,7 @@
         <x:v>1140</x:v>
       </x:c>
       <x:c r="B32" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1909,7 +1909,7 @@
         <x:v>1257</x:v>
       </x:c>
       <x:c r="B33" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1952,7 +1952,7 @@
         <x:v>1163</x:v>
       </x:c>
       <x:c r="B34" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
         <x:v>Core II</x:v>
@@ -1995,7 +1995,7 @@
         <x:v>1221</x:v>
       </x:c>
       <x:c r="B35" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2042,7 +2042,7 @@
         <x:v>2084</x:v>
       </x:c>
       <x:c r="B36" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2085,7 +2085,7 @@
         <x:v>1346</x:v>
       </x:c>
       <x:c r="B37" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2132,7 +2132,7 @@
         <x:v>1415</x:v>
       </x:c>
       <x:c r="B38" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C38" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2181,7 +2181,7 @@
         <x:v>1096</x:v>
       </x:c>
       <x:c r="B39" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>1408</x:v>
       </x:c>
       <x:c r="B40" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C40" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2271,7 +2271,7 @@
         <x:v>1441</x:v>
       </x:c>
       <x:c r="B41" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C41" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2314,7 +2314,7 @@
         <x:v>1402</x:v>
       </x:c>
       <x:c r="B42" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C42" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2359,7 +2359,7 @@
         <x:v>2137</x:v>
       </x:c>
       <x:c r="B43" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C43" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2402,7 +2402,7 @@
         <x:v>1487</x:v>
       </x:c>
       <x:c r="B44" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C44" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2449,7 +2449,7 @@
         <x:v>1299</x:v>
       </x:c>
       <x:c r="B45" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C45" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2496,7 +2496,7 @@
         <x:v>1388</x:v>
       </x:c>
       <x:c r="B46" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C46" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2539,7 +2539,7 @@
         <x:v>1486</x:v>
       </x:c>
       <x:c r="B47" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C47" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2582,7 +2582,7 @@
         <x:v>1544</x:v>
       </x:c>
       <x:c r="B48" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2625,7 +2625,7 @@
         <x:v>1579</x:v>
       </x:c>
       <x:c r="B49" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2670,7 +2670,7 @@
         <x:v>1165</x:v>
       </x:c>
       <x:c r="B50" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2715,7 +2715,7 @@
         <x:v>1425</x:v>
       </x:c>
       <x:c r="B51" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2760,7 +2760,7 @@
         <x:v>1376</x:v>
       </x:c>
       <x:c r="B52" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2803,7 +2803,7 @@
         <x:v>2147</x:v>
       </x:c>
       <x:c r="B53" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2846,7 +2846,7 @@
         <x:v>1770</x:v>
       </x:c>
       <x:c r="B54" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C54" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2889,7 +2889,7 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B55" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C55" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2934,7 +2934,7 @@
         <x:v>1116</x:v>
       </x:c>
       <x:c r="B56" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C56" s="14" t="str">
         <x:v>Core II</x:v>
@@ -2977,7 +2977,7 @@
         <x:v>1286</x:v>
       </x:c>
       <x:c r="B57" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C57" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3020,7 +3020,7 @@
         <x:v>1491</x:v>
       </x:c>
       <x:c r="B58" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C58" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3063,7 +3063,7 @@
         <x:v>1271</x:v>
       </x:c>
       <x:c r="B59" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C59" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3106,7 +3106,7 @@
         <x:v>1587</x:v>
       </x:c>
       <x:c r="B60" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C60" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3151,7 +3151,7 @@
         <x:v>1135</x:v>
       </x:c>
       <x:c r="B61" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C61" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3198,7 +3198,7 @@
         <x:v>1768</x:v>
       </x:c>
       <x:c r="B62" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C62" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3243,7 +3243,7 @@
         <x:v>1322</x:v>
       </x:c>
       <x:c r="B63" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C63" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3286,7 +3286,7 @@
         <x:v>1324</x:v>
       </x:c>
       <x:c r="B64" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C64" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3329,7 +3329,7 @@
         <x:v>1209</x:v>
       </x:c>
       <x:c r="B65" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3372,7 +3372,7 @@
         <x:v>2054</x:v>
       </x:c>
       <x:c r="B66" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C66" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3415,7 +3415,7 @@
         <x:v>1678</x:v>
       </x:c>
       <x:c r="B67" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C67" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3462,7 +3462,7 @@
         <x:v>2118</x:v>
       </x:c>
       <x:c r="B68" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C68" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3505,7 +3505,7 @@
         <x:v>1349</x:v>
       </x:c>
       <x:c r="B69" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C69" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3558,7 +3558,7 @@
         <x:v>1931</x:v>
       </x:c>
       <x:c r="B70" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C70" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3605,7 +3605,7 @@
         <x:v>1458</x:v>
       </x:c>
       <x:c r="B71" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C71" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3650,7 +3650,7 @@
         <x:v>1595</x:v>
       </x:c>
       <x:c r="B72" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C72" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3699,7 +3699,7 @@
         <x:v>1530</x:v>
       </x:c>
       <x:c r="B73" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C73" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3742,7 +3742,7 @@
         <x:v>1887</x:v>
       </x:c>
       <x:c r="B74" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3789,7 +3789,7 @@
         <x:v>1517</x:v>
       </x:c>
       <x:c r="B75" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3836,7 +3836,7 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B76" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3885,7 +3885,7 @@
         <x:v>1114</x:v>
       </x:c>
       <x:c r="B77" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3936,7 +3936,7 @@
         <x:v>1358</x:v>
       </x:c>
       <x:c r="B78" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
         <x:v>Core II</x:v>
@@ -3985,7 +3985,7 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B79" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4032,7 +4032,7 @@
         <x:v>1480</x:v>
       </x:c>
       <x:c r="B80" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4079,7 +4079,7 @@
         <x:v>1208</x:v>
       </x:c>
       <x:c r="B81" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4128,7 +4128,7 @@
         <x:v>1137</x:v>
       </x:c>
       <x:c r="B82" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4175,7 +4175,7 @@
         <x:v>1689</x:v>
       </x:c>
       <x:c r="B83" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4218,7 +4218,7 @@
         <x:v>1478</x:v>
       </x:c>
       <x:c r="B84" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4267,7 +4267,7 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B85" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4312,7 +4312,7 @@
         <x:v>1547</x:v>
       </x:c>
       <x:c r="B86" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C86" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4357,7 +4357,7 @@
         <x:v>1788</x:v>
       </x:c>
       <x:c r="B87" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C87" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4402,7 +4402,7 @@
         <x:v>2105</x:v>
       </x:c>
       <x:c r="B88" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C88" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4447,7 +4447,7 @@
         <x:v>1340</x:v>
       </x:c>
       <x:c r="B89" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C89" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4490,7 +4490,7 @@
         <x:v>2175</x:v>
       </x:c>
       <x:c r="B90" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C90" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4541,7 +4541,7 @@
         <x:v>1205</x:v>
       </x:c>
       <x:c r="B91" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C91" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4584,7 +4584,7 @@
         <x:v>1404</x:v>
       </x:c>
       <x:c r="B92" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C92" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4629,7 +4629,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B93" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C93" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4676,7 +4676,7 @@
         <x:v>1523</x:v>
       </x:c>
       <x:c r="B94" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C94" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4721,7 +4721,7 @@
         <x:v>1236</x:v>
       </x:c>
       <x:c r="B95" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C95" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4766,7 +4766,7 @@
         <x:v>1598</x:v>
       </x:c>
       <x:c r="B96" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C96" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4811,7 +4811,7 @@
         <x:v>2063</x:v>
       </x:c>
       <x:c r="B97" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C97" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4858,7 +4858,7 @@
         <x:v>2065</x:v>
       </x:c>
       <x:c r="B98" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C98" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4907,7 +4907,7 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B99" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C99" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4950,7 +4950,7 @@
         <x:v>1181</x:v>
       </x:c>
       <x:c r="B100" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C100" s="14" t="str">
         <x:v>Core II</x:v>
@@ -4999,7 +4999,7 @@
         <x:v>1725</x:v>
       </x:c>
       <x:c r="B101" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C101" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5042,7 +5042,7 @@
         <x:v>2039</x:v>
       </x:c>
       <x:c r="B102" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C102" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5089,7 +5089,7 @@
         <x:v>1422</x:v>
       </x:c>
       <x:c r="B103" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C103" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5132,7 +5132,7 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B104" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C104" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5179,7 +5179,7 @@
         <x:v>1655</x:v>
       </x:c>
       <x:c r="B105" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C105" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5224,7 +5224,7 @@
         <x:v>1876</x:v>
       </x:c>
       <x:c r="B106" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C106" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5275,7 +5275,7 @@
         <x:v>1960</x:v>
       </x:c>
       <x:c r="B107" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C107" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5318,7 +5318,7 @@
         <x:v>1315</x:v>
       </x:c>
       <x:c r="B108" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C108" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5361,7 +5361,7 @@
         <x:v>1207</x:v>
       </x:c>
       <x:c r="B109" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C109" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5406,7 +5406,7 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B110" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C110" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5449,7 +5449,7 @@
         <x:v>1615</x:v>
       </x:c>
       <x:c r="B111" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C111" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5492,7 +5492,7 @@
         <x:v>1344</x:v>
       </x:c>
       <x:c r="B112" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C112" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5535,7 +5535,7 @@
         <x:v>1179</x:v>
       </x:c>
       <x:c r="B113" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C113" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5578,7 +5578,7 @@
         <x:v>2050</x:v>
       </x:c>
       <x:c r="B114" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C114" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5627,7 +5627,7 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B115" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C115" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5670,7 +5670,7 @@
         <x:v>1794</x:v>
       </x:c>
       <x:c r="B116" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C116" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5717,7 +5717,7 @@
         <x:v>1999</x:v>
       </x:c>
       <x:c r="B117" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C117" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5768,7 +5768,7 @@
         <x:v>1212</x:v>
       </x:c>
       <x:c r="B118" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C118" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5811,7 +5811,7 @@
         <x:v>1813</x:v>
       </x:c>
       <x:c r="B119" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C119" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5854,7 +5854,7 @@
         <x:v>1847</x:v>
       </x:c>
       <x:c r="B120" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C120" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5901,7 +5901,7 @@
         <x:v>1459</x:v>
       </x:c>
       <x:c r="B121" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C121" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5944,7 +5944,7 @@
         <x:v>2029</x:v>
       </x:c>
       <x:c r="B122" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C122" s="14" t="str">
         <x:v>Core II</x:v>
@@ -5991,7 +5991,7 @@
         <x:v>2057</x:v>
       </x:c>
       <x:c r="B123" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C123" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6034,7 +6034,7 @@
         <x:v>1775</x:v>
       </x:c>
       <x:c r="B124" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C124" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6081,7 +6081,7 @@
         <x:v>1584</x:v>
       </x:c>
       <x:c r="B125" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C125" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6126,7 +6126,7 @@
         <x:v>1754</x:v>
       </x:c>
       <x:c r="B126" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C126" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6173,7 +6173,7 @@
         <x:v>1200</x:v>
       </x:c>
       <x:c r="B127" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C127" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6218,7 +6218,7 @@
         <x:v>1548</x:v>
       </x:c>
       <x:c r="B128" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C128" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6261,7 +6261,7 @@
         <x:v>2158</x:v>
       </x:c>
       <x:c r="B129" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C129" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6312,7 +6312,7 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B130" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C130" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6359,7 +6359,7 @@
         <x:v>1739</x:v>
       </x:c>
       <x:c r="B131" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C131" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6406,7 +6406,7 @@
         <x:v>1356</x:v>
       </x:c>
       <x:c r="B132" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C132" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6455,7 +6455,7 @@
         <x:v>2162</x:v>
       </x:c>
       <x:c r="B133" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C133" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6500,7 +6500,7 @@
         <x:v>1711</x:v>
       </x:c>
       <x:c r="B134" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C134" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6547,7 +6547,7 @@
         <x:v>1700</x:v>
       </x:c>
       <x:c r="B135" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C135" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6594,7 +6594,7 @@
         <x:v>1946</x:v>
       </x:c>
       <x:c r="B136" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C136" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6641,7 +6641,7 @@
         <x:v>1499</x:v>
       </x:c>
       <x:c r="B137" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C137" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6688,7 +6688,7 @@
         <x:v>1159</x:v>
       </x:c>
       <x:c r="B138" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C138" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6733,7 +6733,7 @@
         <x:v>1726</x:v>
       </x:c>
       <x:c r="B139" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C139" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6780,7 +6780,7 @@
         <x:v>1475</x:v>
       </x:c>
       <x:c r="B140" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C140" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6829,7 +6829,7 @@
         <x:v>1133</x:v>
       </x:c>
       <x:c r="B141" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C141" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6872,7 +6872,7 @@
         <x:v>1653</x:v>
       </x:c>
       <x:c r="B142" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C142" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6917,7 +6917,7 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B143" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C143" s="14" t="str">
         <x:v>Core II</x:v>
@@ -6968,7 +6968,7 @@
         <x:v>1502</x:v>
       </x:c>
       <x:c r="B144" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C144" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7011,7 +7011,7 @@
         <x:v>1440</x:v>
       </x:c>
       <x:c r="B145" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C145" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7054,7 +7054,7 @@
         <x:v>1482</x:v>
       </x:c>
       <x:c r="B146" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C146" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7097,7 +7097,7 @@
         <x:v>2140</x:v>
       </x:c>
       <x:c r="B147" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C147" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7144,7 +7144,7 @@
         <x:v>1147</x:v>
       </x:c>
       <x:c r="B148" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C148" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7193,7 +7193,7 @@
         <x:v>1629</x:v>
       </x:c>
       <x:c r="B149" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C149" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7240,7 +7240,7 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B150" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C150" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7287,7 +7287,7 @@
         <x:v>1641</x:v>
       </x:c>
       <x:c r="B151" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C151" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7332,7 +7332,7 @@
         <x:v>2044</x:v>
       </x:c>
       <x:c r="B152" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C152" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7379,7 +7379,7 @@
         <x:v>1925</x:v>
       </x:c>
       <x:c r="B153" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C153" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7422,7 +7422,7 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="B154" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C154" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7465,7 +7465,7 @@
         <x:v>2154</x:v>
       </x:c>
       <x:c r="B155" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C155" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7512,7 +7512,7 @@
         <x:v>1519</x:v>
       </x:c>
       <x:c r="B156" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C156" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7555,7 +7555,7 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B157" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C157" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7598,7 +7598,7 @@
         <x:v>1371</x:v>
       </x:c>
       <x:c r="B158" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C158" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7645,7 +7645,7 @@
         <x:v>1497</x:v>
       </x:c>
       <x:c r="B159" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C159" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7688,7 +7688,7 @@
         <x:v>1685</x:v>
       </x:c>
       <x:c r="B160" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C160" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7739,7 +7739,7 @@
         <x:v>1091</x:v>
       </x:c>
       <x:c r="B161" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C161" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7784,7 +7784,7 @@
         <x:v>2099</x:v>
       </x:c>
       <x:c r="B162" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C162" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7835,7 +7835,7 @@
         <x:v>1728</x:v>
       </x:c>
       <x:c r="B163" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C163" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7880,7 +7880,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="B164" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C164" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7927,7 +7927,7 @@
         <x:v>1216</x:v>
       </x:c>
       <x:c r="B165" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C165" s="14" t="str">
         <x:v>Core II</x:v>
@@ -7972,7 +7972,7 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B166" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C166" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8019,7 +8019,7 @@
         <x:v>1955</x:v>
       </x:c>
       <x:c r="B167" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C167" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8062,7 +8062,7 @@
         <x:v>1120</x:v>
       </x:c>
       <x:c r="B168" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C168" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8107,7 +8107,7 @@
         <x:v>1412</x:v>
       </x:c>
       <x:c r="B169" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C169" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8154,7 +8154,7 @@
         <x:v>1407</x:v>
       </x:c>
       <x:c r="B170" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C170" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8197,7 +8197,7 @@
         <x:v>1262</x:v>
       </x:c>
       <x:c r="B171" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C171" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8242,7 +8242,7 @@
         <x:v>1627</x:v>
       </x:c>
       <x:c r="B172" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C172" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8289,7 +8289,7 @@
         <x:v>1878</x:v>
       </x:c>
       <x:c r="B173" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C173" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8336,7 +8336,7 @@
         <x:v>1129</x:v>
       </x:c>
       <x:c r="B174" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C174" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8379,7 +8379,7 @@
         <x:v>1757</x:v>
       </x:c>
       <x:c r="B175" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C175" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8426,7 +8426,7 @@
         <x:v>1822</x:v>
       </x:c>
       <x:c r="B176" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C176" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8473,7 +8473,7 @@
         <x:v>1495</x:v>
       </x:c>
       <x:c r="B177" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C177" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8520,7 +8520,7 @@
         <x:v>1420</x:v>
       </x:c>
       <x:c r="B178" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C178" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8563,7 +8563,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="B179" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C179" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8608,7 +8608,7 @@
         <x:v>1263</x:v>
       </x:c>
       <x:c r="B180" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C180" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8653,7 +8653,7 @@
         <x:v>1424</x:v>
       </x:c>
       <x:c r="B181" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C181" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8696,7 +8696,7 @@
         <x:v>2167</x:v>
       </x:c>
       <x:c r="B182" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C182" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8743,7 +8743,7 @@
         <x:v>1148</x:v>
       </x:c>
       <x:c r="B183" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C183" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8788,7 +8788,7 @@
         <x:v>1240</x:v>
       </x:c>
       <x:c r="B184" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C184" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8831,7 +8831,7 @@
         <x:v>2109</x:v>
       </x:c>
       <x:c r="B185" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C185" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8874,7 +8874,7 @@
         <x:v>1880</x:v>
       </x:c>
       <x:c r="B186" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C186" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8923,7 +8923,7 @@
         <x:v>1877</x:v>
       </x:c>
       <x:c r="B187" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C187" s="14" t="str">
         <x:v>Core II</x:v>
@@ -8974,7 +8974,7 @@
         <x:v>2021</x:v>
       </x:c>
       <x:c r="B188" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C188" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9017,7 +9017,7 @@
         <x:v>2020</x:v>
       </x:c>
       <x:c r="B189" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C189" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9060,7 +9060,7 @@
         <x:v>1793</x:v>
       </x:c>
       <x:c r="B190" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C190" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9107,7 +9107,7 @@
         <x:v>1881</x:v>
       </x:c>
       <x:c r="B191" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C191" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9156,7 +9156,7 @@
         <x:v>1520</x:v>
       </x:c>
       <x:c r="B192" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C192" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9199,7 +9199,7 @@
         <x:v>1715</x:v>
       </x:c>
       <x:c r="B193" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C193" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9244,7 +9244,7 @@
         <x:v>1872</x:v>
       </x:c>
       <x:c r="B194" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C194" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9287,7 +9287,7 @@
         <x:v>1305</x:v>
       </x:c>
       <x:c r="B195" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C195" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9330,7 +9330,7 @@
         <x:v>2123</x:v>
       </x:c>
       <x:c r="B196" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C196" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9373,7 +9373,7 @@
         <x:v>1957</x:v>
       </x:c>
       <x:c r="B197" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C197" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9418,7 +9418,7 @@
         <x:v>1729</x:v>
       </x:c>
       <x:c r="B198" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C198" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9465,7 +9465,7 @@
         <x:v>1886</x:v>
       </x:c>
       <x:c r="B199" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C199" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9508,7 +9508,7 @@
         <x:v>1649</x:v>
       </x:c>
       <x:c r="B200" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C200" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9553,7 +9553,7 @@
         <x:v>1874</x:v>
       </x:c>
       <x:c r="B201" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C201" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9602,7 +9602,7 @@
         <x:v>2014</x:v>
       </x:c>
       <x:c r="B202" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C202" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9651,7 +9651,7 @@
         <x:v>1387</x:v>
       </x:c>
       <x:c r="B203" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C203" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9694,7 +9694,7 @@
         <x:v>2027</x:v>
       </x:c>
       <x:c r="B204" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C204" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9737,7 +9737,7 @@
         <x:v>1522</x:v>
       </x:c>
       <x:c r="B205" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C205" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9790,7 +9790,7 @@
         <x:v>1934</x:v>
       </x:c>
       <x:c r="B206" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C206" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9833,7 +9833,7 @@
         <x:v>1597</x:v>
       </x:c>
       <x:c r="B207" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C207" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9878,7 +9878,7 @@
         <x:v>1643</x:v>
       </x:c>
       <x:c r="B208" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C208" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9923,7 +9923,7 @@
         <x:v>1258</x:v>
       </x:c>
       <x:c r="B209" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C209" s="14" t="str">
         <x:v>Core II</x:v>
@@ -9966,7 +9966,7 @@
         <x:v>2035</x:v>
       </x:c>
       <x:c r="B210" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C210" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10021,7 +10021,7 @@
         <x:v>1224</x:v>
       </x:c>
       <x:c r="B211" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C211" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10068,7 +10068,7 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B212" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C212" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10113,7 +10113,7 @@
         <x:v>1740</x:v>
       </x:c>
       <x:c r="B213" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C213" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10160,7 +10160,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B214" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C214" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10203,7 +10203,7 @@
         <x:v>2024</x:v>
       </x:c>
       <x:c r="B215" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C215" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10254,7 +10254,7 @@
         <x:v>1909</x:v>
       </x:c>
       <x:c r="B216" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C216" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10303,7 +10303,7 @@
         <x:v>1823</x:v>
       </x:c>
       <x:c r="B217" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C217" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10350,7 +10350,7 @@
         <x:v>2043</x:v>
       </x:c>
       <x:c r="B218" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C218" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10393,7 +10393,7 @@
         <x:v>1166</x:v>
       </x:c>
       <x:c r="B219" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C219" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10438,7 +10438,7 @@
         <x:v>1594</x:v>
       </x:c>
       <x:c r="B220" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C220" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10481,7 +10481,7 @@
         <x:v>1343</x:v>
       </x:c>
       <x:c r="B221" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C221" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10528,7 +10528,7 @@
         <x:v>1893</x:v>
       </x:c>
       <x:c r="B222" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C222" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10577,7 +10577,7 @@
         <x:v>1623</x:v>
       </x:c>
       <x:c r="B223" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C223" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10624,7 +10624,7 @@
         <x:v>1849</x:v>
       </x:c>
       <x:c r="B224" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C224" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10671,7 +10671,7 @@
         <x:v>1229</x:v>
       </x:c>
       <x:c r="B225" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C225" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10714,7 +10714,7 @@
         <x:v>1538</x:v>
       </x:c>
       <x:c r="B226" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C226" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10761,7 +10761,7 @@
         <x:v>1928</x:v>
       </x:c>
       <x:c r="B227" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C227" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10808,7 +10808,7 @@
         <x:v>1787</x:v>
       </x:c>
       <x:c r="B228" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C228" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10853,7 +10853,7 @@
         <x:v>2150</x:v>
       </x:c>
       <x:c r="B229" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C229" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10900,7 +10900,7 @@
         <x:v>2076</x:v>
       </x:c>
       <x:c r="B230" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C230" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10945,7 +10945,7 @@
         <x:v>1751</x:v>
       </x:c>
       <x:c r="B231" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C231" s="14" t="str">
         <x:v>Core II</x:v>
@@ -10988,7 +10988,7 @@
         <x:v>1589</x:v>
       </x:c>
       <x:c r="B232" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C232" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11033,7 +11033,7 @@
         <x:v>1669</x:v>
       </x:c>
       <x:c r="B233" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C233" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11076,7 +11076,7 @@
         <x:v>1747</x:v>
       </x:c>
       <x:c r="B234" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C234" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11119,7 +11119,7 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B235" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C235" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11162,7 +11162,7 @@
         <x:v>1866</x:v>
       </x:c>
       <x:c r="B236" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C236" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11211,7 +11211,7 @@
         <x:v>1366</x:v>
       </x:c>
       <x:c r="B237" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C237" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11254,7 +11254,7 @@
         <x:v>1621</x:v>
       </x:c>
       <x:c r="B238" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C238" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11301,7 +11301,7 @@
         <x:v>2055</x:v>
       </x:c>
       <x:c r="B239" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C239" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11344,7 +11344,7 @@
         <x:v>1512</x:v>
       </x:c>
       <x:c r="B240" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C240" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11387,7 +11387,7 @@
         <x:v>1913</x:v>
       </x:c>
       <x:c r="B241" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C241" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11432,7 +11432,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="B242" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C242" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11479,7 +11479,7 @@
         <x:v>1924</x:v>
       </x:c>
       <x:c r="B243" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C243" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11528,7 +11528,7 @@
         <x:v>1966</x:v>
       </x:c>
       <x:c r="B244" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C244" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11581,7 +11581,7 @@
         <x:v>1824</x:v>
       </x:c>
       <x:c r="B245" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C245" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11628,7 +11628,7 @@
         <x:v>1280</x:v>
       </x:c>
       <x:c r="B246" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C246" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11675,7 +11675,7 @@
         <x:v>2090</x:v>
       </x:c>
       <x:c r="B247" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C247" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11722,7 +11722,7 @@
         <x:v>1264</x:v>
       </x:c>
       <x:c r="B248" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C248" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11767,7 +11767,7 @@
         <x:v>1766</x:v>
       </x:c>
       <x:c r="B249" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C249" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11810,7 +11810,7 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B250" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C250" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11865,7 +11865,7 @@
         <x:v>2046</x:v>
       </x:c>
       <x:c r="B251" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C251" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11910,7 +11910,7 @@
         <x:v>1710</x:v>
       </x:c>
       <x:c r="B252" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C252" s="14" t="str">
         <x:v>Core II</x:v>
@@ -11955,7 +11955,7 @@
         <x:v>1763</x:v>
       </x:c>
       <x:c r="B253" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C253" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12004,7 +12004,7 @@
         <x:v>1614</x:v>
       </x:c>
       <x:c r="B254" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C254" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12049,7 +12049,7 @@
         <x:v>1350</x:v>
       </x:c>
       <x:c r="B255" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C255" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12102,7 +12102,7 @@
         <x:v>1307</x:v>
       </x:c>
       <x:c r="B256" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C256" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12145,7 +12145,7 @@
         <x:v>1697</x:v>
       </x:c>
       <x:c r="B257" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C257" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12194,7 +12194,7 @@
         <x:v>1261</x:v>
       </x:c>
       <x:c r="B258" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C258" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12239,7 +12239,7 @@
         <x:v>1249</x:v>
       </x:c>
       <x:c r="B259" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C259" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12284,7 +12284,7 @@
         <x:v>2059</x:v>
       </x:c>
       <x:c r="B260" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C260" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12331,7 +12331,7 @@
         <x:v>1884</x:v>
       </x:c>
       <x:c r="B261" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C261" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12380,7 +12380,7 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B262" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C262" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12423,7 +12423,7 @@
         <x:v>2086</x:v>
       </x:c>
       <x:c r="B263" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C263" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12470,7 +12470,7 @@
         <x:v>1801</x:v>
       </x:c>
       <x:c r="B264" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C264" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12519,7 +12519,7 @@
         <x:v>1625</x:v>
       </x:c>
       <x:c r="B265" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C265" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12562,7 +12562,7 @@
         <x:v>1521</x:v>
       </x:c>
       <x:c r="B266" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C266" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12605,7 +12605,7 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="B267" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C267" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12656,7 +12656,7 @@
         <x:v>1882</x:v>
       </x:c>
       <x:c r="B268" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C268" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12703,7 +12703,7 @@
         <x:v>1885</x:v>
       </x:c>
       <x:c r="B269" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C269" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12750,7 +12750,7 @@
         <x:v>1308</x:v>
       </x:c>
       <x:c r="B270" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C270" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12793,7 +12793,7 @@
         <x:v>1646</x:v>
       </x:c>
       <x:c r="B271" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C271" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12838,7 +12838,7 @@
         <x:v>1686</x:v>
       </x:c>
       <x:c r="B272" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C272" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12881,7 +12881,7 @@
         <x:v>1177</x:v>
       </x:c>
       <x:c r="B273" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C273" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12926,7 +12926,7 @@
         <x:v>1535</x:v>
       </x:c>
       <x:c r="B274" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C274" s="14" t="str">
         <x:v>Core II</x:v>
@@ -12981,7 +12981,7 @@
         <x:v>2074</x:v>
       </x:c>
       <x:c r="B275" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C275" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13026,7 +13026,7 @@
         <x:v>1542</x:v>
       </x:c>
       <x:c r="B276" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C276" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13073,7 +13073,7 @@
         <x:v>1919</x:v>
       </x:c>
       <x:c r="B277" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C277" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13126,7 +13126,7 @@
         <x:v>2058</x:v>
       </x:c>
       <x:c r="B278" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C278" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13177,7 +13177,7 @@
         <x:v>1567</x:v>
       </x:c>
       <x:c r="B279" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C279" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13224,7 +13224,7 @@
         <x:v>1836</x:v>
       </x:c>
       <x:c r="B280" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C280" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13273,7 +13273,7 @@
         <x:v>2121</x:v>
       </x:c>
       <x:c r="B281" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C281" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13322,7 +13322,7 @@
         <x:v>1199</x:v>
       </x:c>
       <x:c r="B282" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C282" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13367,7 +13367,7 @@
         <x:v>1414</x:v>
       </x:c>
       <x:c r="B283" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C283" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13412,7 +13412,7 @@
         <x:v>1693</x:v>
       </x:c>
       <x:c r="B284" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C284" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13455,7 +13455,7 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B285" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C285" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13500,7 +13500,7 @@
         <x:v>2160</x:v>
       </x:c>
       <x:c r="B286" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C286" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13545,7 +13545,7 @@
         <x:v>1484</x:v>
       </x:c>
       <x:c r="B287" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C287" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13588,7 +13588,7 @@
         <x:v>1406</x:v>
       </x:c>
       <x:c r="B288" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C288" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13637,7 +13637,7 @@
         <x:v>1772</x:v>
       </x:c>
       <x:c r="B289" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C289" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13682,7 +13682,7 @@
         <x:v>1951</x:v>
       </x:c>
       <x:c r="B290" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C290" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13729,7 +13729,7 @@
         <x:v>1167</x:v>
       </x:c>
       <x:c r="B291" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C291" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13774,7 +13774,7 @@
         <x:v>1912</x:v>
       </x:c>
       <x:c r="B292" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C292" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13819,7 +13819,7 @@
         <x:v>1883</x:v>
       </x:c>
       <x:c r="B293" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C293" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13868,7 +13868,7 @@
         <x:v>1423</x:v>
       </x:c>
       <x:c r="B294" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C294" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13911,7 +13911,7 @@
         <x:v>1760</x:v>
       </x:c>
       <x:c r="B295" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C295" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13954,7 +13954,7 @@
         <x:v>1184</x:v>
       </x:c>
       <x:c r="B296" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C296" s="14" t="str">
         <x:v>Core II</x:v>
@@ -13997,7 +13997,7 @@
         <x:v>2034</x:v>
       </x:c>
       <x:c r="B297" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C297" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14042,7 +14042,7 @@
         <x:v>1161</x:v>
       </x:c>
       <x:c r="B298" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C298" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14087,7 +14087,7 @@
         <x:v>1098</x:v>
       </x:c>
       <x:c r="B299" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C299" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14140,7 +14140,7 @@
         <x:v>1401</x:v>
       </x:c>
       <x:c r="B300" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C300" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14185,7 +14185,7 @@
         <x:v>1157</x:v>
       </x:c>
       <x:c r="B301" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C301" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14230,7 +14230,7 @@
         <x:v>1858</x:v>
       </x:c>
       <x:c r="B302" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C302" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14283,7 +14283,7 @@
         <x:v>1862</x:v>
       </x:c>
       <x:c r="B303" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C303" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14326,7 +14326,7 @@
         <x:v>1203</x:v>
       </x:c>
       <x:c r="B304" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C304" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14371,7 +14371,7 @@
         <x:v>1293</x:v>
       </x:c>
       <x:c r="B305" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C305" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14414,7 +14414,7 @@
         <x:v>1431</x:v>
       </x:c>
       <x:c r="B306" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C306" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14457,7 +14457,7 @@
         <x:v>1375</x:v>
       </x:c>
       <x:c r="B307" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C307" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14500,7 +14500,7 @@
         <x:v>1570</x:v>
       </x:c>
       <x:c r="B308" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C308" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14543,7 +14543,7 @@
         <x:v>1244</x:v>
       </x:c>
       <x:c r="B309" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C309" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14592,7 +14592,7 @@
         <x:v>2080</x:v>
       </x:c>
       <x:c r="B310" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C310" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14639,7 +14639,7 @@
         <x:v>1153</x:v>
       </x:c>
       <x:c r="B311" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C311" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14686,7 +14686,7 @@
         <x:v>1696</x:v>
       </x:c>
       <x:c r="B312" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C312" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14729,7 +14729,7 @@
         <x:v>1576</x:v>
       </x:c>
       <x:c r="B313" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C313" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14782,7 +14782,7 @@
         <x:v>1233</x:v>
       </x:c>
       <x:c r="B314" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C314" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14827,7 +14827,7 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B315" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C315" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14870,7 +14870,7 @@
         <x:v>1795</x:v>
       </x:c>
       <x:c r="B316" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C316" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14913,7 +14913,7 @@
         <x:v>1906</x:v>
       </x:c>
       <x:c r="B317" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C317" s="14" t="str">
         <x:v>Core II</x:v>
@@ -14966,7 +14966,7 @@
         <x:v>1674</x:v>
       </x:c>
       <x:c r="B318" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C318" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15009,7 +15009,7 @@
         <x:v>1411</x:v>
       </x:c>
       <x:c r="B319" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C319" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15058,7 +15058,7 @@
         <x:v>1508</x:v>
       </x:c>
       <x:c r="B320" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C320" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15105,7 +15105,7 @@
         <x:v>1219</x:v>
       </x:c>
       <x:c r="B321" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C321" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15150,7 +15150,7 @@
         <x:v>1476</x:v>
       </x:c>
       <x:c r="B322" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C322" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15193,7 +15193,7 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="B323" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C323" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15238,7 +15238,7 @@
         <x:v>1395</x:v>
       </x:c>
       <x:c r="B324" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C324" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15283,7 +15283,7 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B325" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C325" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15330,7 +15330,7 @@
         <x:v>1592</x:v>
       </x:c>
       <x:c r="B326" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C326" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15377,7 +15377,7 @@
         <x:v>1362</x:v>
       </x:c>
       <x:c r="B327" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C327" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15420,7 +15420,7 @@
         <x:v>1656</x:v>
       </x:c>
       <x:c r="B328" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C328" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15463,7 +15463,7 @@
         <x:v>2036</x:v>
       </x:c>
       <x:c r="B329" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C329" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15516,7 +15516,7 @@
         <x:v>1613</x:v>
       </x:c>
       <x:c r="B330" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C330" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15561,7 +15561,7 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B331" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C331" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15608,7 +15608,7 @@
         <x:v>1658</x:v>
       </x:c>
       <x:c r="B332" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C332" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15651,7 +15651,7 @@
         <x:v>1107</x:v>
       </x:c>
       <x:c r="B333" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C333" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15700,7 +15700,7 @@
         <x:v>1706</x:v>
       </x:c>
       <x:c r="B334" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C334" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15747,7 +15747,7 @@
         <x:v>2018</x:v>
       </x:c>
       <x:c r="B335" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C335" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15794,7 +15794,7 @@
         <x:v>1712</x:v>
       </x:c>
       <x:c r="B336" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C336" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15841,7 +15841,7 @@
         <x:v>1105</x:v>
       </x:c>
       <x:c r="B337" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C337" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15890,7 +15890,7 @@
         <x:v>1731</x:v>
       </x:c>
       <x:c r="B338" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C338" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15935,7 +15935,7 @@
         <x:v>1396</x:v>
       </x:c>
       <x:c r="B339" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C339" s="14" t="str">
         <x:v>Core II</x:v>
@@ -15980,7 +15980,7 @@
         <x:v>1995</x:v>
       </x:c>
       <x:c r="B340" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C340" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16023,7 +16023,7 @@
         <x:v>1707</x:v>
       </x:c>
       <x:c r="B341" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C341" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16066,7 +16066,7 @@
         <x:v>1904</x:v>
       </x:c>
       <x:c r="B342" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C342" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16119,7 +16119,7 @@
         <x:v>1997</x:v>
       </x:c>
       <x:c r="B343" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C343" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16170,7 +16170,7 @@
         <x:v>1310</x:v>
       </x:c>
       <x:c r="B344" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C344" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16215,7 +16215,7 @@
         <x:v>1494</x:v>
       </x:c>
       <x:c r="B345" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C345" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16258,7 +16258,7 @@
         <x:v>1733</x:v>
       </x:c>
       <x:c r="B346" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C346" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16313,7 +16313,7 @@
         <x:v>1962</x:v>
       </x:c>
       <x:c r="B347" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C347" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16360,7 +16360,7 @@
         <x:v>1247</x:v>
       </x:c>
       <x:c r="B348" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C348" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16403,7 +16403,7 @@
         <x:v>1492</x:v>
       </x:c>
       <x:c r="B349" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C349" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16450,7 +16450,7 @@
         <x:v>1805</x:v>
       </x:c>
       <x:c r="B350" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C350" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16497,7 +16497,7 @@
         <x:v>2048</x:v>
       </x:c>
       <x:c r="B351" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C351" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16542,7 +16542,7 @@
         <x:v>1533</x:v>
       </x:c>
       <x:c r="B352" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C352" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16593,7 +16593,7 @@
         <x:v>2165</x:v>
       </x:c>
       <x:c r="B353" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C353" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16640,7 +16640,7 @@
         <x:v>1149</x:v>
       </x:c>
       <x:c r="B354" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C354" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16685,7 +16685,7 @@
         <x:v>2077</x:v>
       </x:c>
       <x:c r="B355" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C355" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16736,7 +16736,7 @@
         <x:v>2172</x:v>
       </x:c>
       <x:c r="B356" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C356" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16789,7 +16789,7 @@
         <x:v>1694</x:v>
       </x:c>
       <x:c r="B357" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C357" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16832,7 +16832,7 @@
         <x:v>1580</x:v>
       </x:c>
       <x:c r="B358" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C358" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16877,7 +16877,7 @@
         <x:v>1720</x:v>
       </x:c>
       <x:c r="B359" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C359" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16922,7 +16922,7 @@
         <x:v>1574</x:v>
       </x:c>
       <x:c r="B360" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C360" s="14" t="str">
         <x:v>Core II</x:v>
@@ -16965,7 +16965,7 @@
         <x:v>1119</x:v>
       </x:c>
       <x:c r="B361" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C361" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17010,7 +17010,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="B362" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C362" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17059,7 +17059,7 @@
         <x:v>1287</x:v>
       </x:c>
       <x:c r="B363" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C363" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17104,7 +17104,7 @@
         <x:v>1973</x:v>
       </x:c>
       <x:c r="B364" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C364" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17151,7 +17151,7 @@
         <x:v>1143</x:v>
       </x:c>
       <x:c r="B365" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C365" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17200,7 +17200,7 @@
         <x:v>1981</x:v>
       </x:c>
       <x:c r="B366" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C366" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17247,7 +17247,7 @@
         <x:v>1781</x:v>
       </x:c>
       <x:c r="B367" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C367" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17290,7 +17290,7 @@
         <x:v>1427</x:v>
       </x:c>
       <x:c r="B368" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C368" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17337,7 +17337,7 @@
         <x:v>2009</x:v>
       </x:c>
       <x:c r="B369" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C369" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17384,7 +17384,7 @@
         <x:v>1092</x:v>
       </x:c>
       <x:c r="B370" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C370" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17431,7 +17431,7 @@
         <x:v>1907</x:v>
       </x:c>
       <x:c r="B371" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C371" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17484,7 +17484,7 @@
         <x:v>1900</x:v>
       </x:c>
       <x:c r="B372" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C372" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17527,7 +17527,7 @@
         <x:v>1843</x:v>
       </x:c>
       <x:c r="B373" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C373" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17570,7 +17570,7 @@
         <x:v>1501</x:v>
       </x:c>
       <x:c r="B374" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C374" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17615,7 +17615,7 @@
         <x:v>1652</x:v>
       </x:c>
       <x:c r="B375" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C375" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17660,7 +17660,7 @@
         <x:v>2159</x:v>
       </x:c>
       <x:c r="B376" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C376" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17705,7 +17705,7 @@
         <x:v>1681</x:v>
       </x:c>
       <x:c r="B377" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C377" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17750,7 +17750,7 @@
         <x:v>1617</x:v>
       </x:c>
       <x:c r="B378" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C378" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17795,7 +17795,7 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B379" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C379" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17840,7 +17840,7 @@
         <x:v>1988</x:v>
       </x:c>
       <x:c r="B380" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C380" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17891,7 +17891,7 @@
         <x:v>1687</x:v>
       </x:c>
       <x:c r="B381" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C381" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17936,7 +17936,7 @@
         <x:v>1736</x:v>
       </x:c>
       <x:c r="B382" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C382" s="14" t="str">
         <x:v>Core II</x:v>
@@ -17983,7 +17983,7 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B383" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C383" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18028,7 +18028,7 @@
         <x:v>1444</x:v>
       </x:c>
       <x:c r="B384" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C384" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18073,7 +18073,7 @@
         <x:v>1197</x:v>
       </x:c>
       <x:c r="B385" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C385" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18118,7 +18118,7 @@
         <x:v>1590</x:v>
       </x:c>
       <x:c r="B386" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C386" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18163,7 +18163,7 @@
         <x:v>1846</x:v>
       </x:c>
       <x:c r="B387" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C387" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18210,7 +18210,7 @@
         <x:v>1288</x:v>
       </x:c>
       <x:c r="B388" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C388" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18255,7 +18255,7 @@
         <x:v>1231</x:v>
       </x:c>
       <x:c r="B389" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C389" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18302,7 +18302,7 @@
         <x:v>1348</x:v>
       </x:c>
       <x:c r="B390" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C390" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18355,7 +18355,7 @@
         <x:v>2061</x:v>
       </x:c>
       <x:c r="B391" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C391" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18402,7 +18402,7 @@
         <x:v>1608</x:v>
       </x:c>
       <x:c r="B392" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C392" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18445,7 +18445,7 @@
         <x:v>1529</x:v>
       </x:c>
       <x:c r="B393" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C393" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18490,7 +18490,7 @@
         <x:v>1807</x:v>
       </x:c>
       <x:c r="B394" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C394" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18535,7 +18535,7 @@
         <x:v>1820</x:v>
       </x:c>
       <x:c r="B395" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C395" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18584,7 +18584,7 @@
         <x:v>2128</x:v>
       </x:c>
       <x:c r="B396" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C396" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18639,7 +18639,7 @@
         <x:v>1826</x:v>
       </x:c>
       <x:c r="B397" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C397" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18682,7 +18682,7 @@
         <x:v>1554</x:v>
       </x:c>
       <x:c r="B398" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C398" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18727,7 +18727,7 @@
         <x:v>1545</x:v>
       </x:c>
       <x:c r="B399" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C399" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18770,7 +18770,7 @@
         <x:v>1891</x:v>
       </x:c>
       <x:c r="B400" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C400" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18815,7 +18815,7 @@
         <x:v>2087</x:v>
       </x:c>
       <x:c r="B401" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C401" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18862,7 +18862,7 @@
         <x:v>1800</x:v>
       </x:c>
       <x:c r="B402" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C402" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18911,7 +18911,7 @@
         <x:v>1611</x:v>
       </x:c>
       <x:c r="B403" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C403" s="14" t="str">
         <x:v>Core II</x:v>
@@ -18956,7 +18956,7 @@
         <x:v>1797</x:v>
       </x:c>
       <x:c r="B404" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C404" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19003,7 +19003,7 @@
         <x:v>1152</x:v>
       </x:c>
       <x:c r="B405" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C405" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19048,7 +19048,7 @@
         <x:v>1453</x:v>
       </x:c>
       <x:c r="B406" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C406" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19093,7 +19093,7 @@
         <x:v>1260</x:v>
       </x:c>
       <x:c r="B407" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C407" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19138,7 +19138,7 @@
         <x:v>1306</x:v>
       </x:c>
       <x:c r="B408" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C408" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19181,7 +19181,7 @@
         <x:v>1253</x:v>
       </x:c>
       <x:c r="B409" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C409" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19224,7 +19224,7 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B410" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C410" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19271,7 +19271,7 @@
         <x:v>1446</x:v>
       </x:c>
       <x:c r="B411" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C411" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19316,7 +19316,7 @@
         <x:v>1525</x:v>
       </x:c>
       <x:c r="B412" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C412" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19361,7 +19361,7 @@
         <x:v>1842</x:v>
       </x:c>
       <x:c r="B413" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C413" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19404,7 +19404,7 @@
         <x:v>1468</x:v>
       </x:c>
       <x:c r="B414" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C414" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19447,7 +19447,7 @@
         <x:v>1827</x:v>
       </x:c>
       <x:c r="B415" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C415" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19498,7 +19498,7 @@
         <x:v>2164</x:v>
       </x:c>
       <x:c r="B416" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C416" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19545,7 +19545,7 @@
         <x:v>1445</x:v>
       </x:c>
       <x:c r="B417" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C417" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19590,7 +19590,7 @@
         <x:v>1975</x:v>
       </x:c>
       <x:c r="B418" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C418" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19637,7 +19637,7 @@
         <x:v>1940</x:v>
       </x:c>
       <x:c r="B419" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C419" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19684,7 +19684,7 @@
         <x:v>1290</x:v>
       </x:c>
       <x:c r="B420" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C420" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19733,7 +19733,7 @@
         <x:v>1809</x:v>
       </x:c>
       <x:c r="B421" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C421" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19778,7 +19778,7 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B422" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C422" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19831,7 +19831,7 @@
         <x:v>2156</x:v>
       </x:c>
       <x:c r="B423" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C423" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19878,7 +19878,7 @@
         <x:v>1524</x:v>
       </x:c>
       <x:c r="B424" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C424" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19923,7 +19923,7 @@
         <x:v>1560</x:v>
       </x:c>
       <x:c r="B425" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C425" s="14" t="str">
         <x:v>Core II</x:v>
@@ -19966,7 +19966,7 @@
         <x:v>2130</x:v>
       </x:c>
       <x:c r="B426" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C426" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20009,7 +20009,7 @@
         <x:v>1628</x:v>
       </x:c>
       <x:c r="B427" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C427" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20054,7 +20054,7 @@
         <x:v>1804</x:v>
       </x:c>
       <x:c r="B428" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C428" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20097,7 +20097,7 @@
         <x:v>1122</x:v>
       </x:c>
       <x:c r="B429" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C429" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20146,7 +20146,7 @@
         <x:v>1958</x:v>
       </x:c>
       <x:c r="B430" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C430" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20191,7 +20191,7 @@
         <x:v>1735</x:v>
       </x:c>
       <x:c r="B431" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C431" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20234,7 +20234,7 @@
         <x:v>1374</x:v>
       </x:c>
       <x:c r="B432" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C432" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20281,7 +20281,7 @@
         <x:v>1416</x:v>
       </x:c>
       <x:c r="B433" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C433" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20330,7 +20330,7 @@
         <x:v>1418</x:v>
       </x:c>
       <x:c r="B434" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C434" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20373,7 +20373,7 @@
         <x:v>1865</x:v>
       </x:c>
       <x:c r="B435" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C435" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20422,7 +20422,7 @@
         <x:v>1654</x:v>
       </x:c>
       <x:c r="B436" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C436" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20467,7 +20467,7 @@
         <x:v>2038</x:v>
       </x:c>
       <x:c r="B437" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C437" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20510,7 +20510,7 @@
         <x:v>2166</x:v>
       </x:c>
       <x:c r="B438" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C438" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20563,7 +20563,7 @@
         <x:v>2053</x:v>
       </x:c>
       <x:c r="B439" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C439" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20610,7 +20610,7 @@
         <x:v>1516</x:v>
       </x:c>
       <x:c r="B440" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C440" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20657,7 +20657,7 @@
         <x:v>1154</x:v>
       </x:c>
       <x:c r="B441" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C441" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20700,7 +20700,7 @@
         <x:v>1923</x:v>
       </x:c>
       <x:c r="B442" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C442" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20749,7 +20749,7 @@
         <x:v>2107</x:v>
       </x:c>
       <x:c r="B443" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C443" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20792,7 +20792,7 @@
         <x:v>1908</x:v>
       </x:c>
       <x:c r="B444" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C444" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20837,7 +20837,7 @@
         <x:v>2108</x:v>
       </x:c>
       <x:c r="B445" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C445" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20882,7 +20882,7 @@
         <x:v>2081</x:v>
       </x:c>
       <x:c r="B446" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C446" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20925,7 +20925,7 @@
         <x:v>1339</x:v>
       </x:c>
       <x:c r="B447" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C447" s="14" t="str">
         <x:v>Core II</x:v>
@@ -20968,7 +20968,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="B448" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C448" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21013,7 +21013,7 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B449" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C449" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21060,7 +21060,7 @@
         <x:v>1578</x:v>
       </x:c>
       <x:c r="B450" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C450" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21105,7 +21105,7 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B451" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C451" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21158,7 +21158,7 @@
         <x:v>1699</x:v>
       </x:c>
       <x:c r="B452" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C452" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21203,7 +21203,7 @@
         <x:v>1537</x:v>
       </x:c>
       <x:c r="B453" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C453" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21250,7 +21250,7 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B454" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C454" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21297,7 +21297,7 @@
         <x:v>1386</x:v>
       </x:c>
       <x:c r="B455" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C455" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21340,7 +21340,7 @@
         <x:v>1379</x:v>
       </x:c>
       <x:c r="B456" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C456" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21383,7 +21383,7 @@
         <x:v>1210</x:v>
       </x:c>
       <x:c r="B457" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C457" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21430,7 +21430,7 @@
         <x:v>2104</x:v>
       </x:c>
       <x:c r="B458" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C458" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21483,7 +21483,7 @@
         <x:v>2149</x:v>
       </x:c>
       <x:c r="B459" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C459" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21530,7 +21530,7 @@
         <x:v>1454</x:v>
       </x:c>
       <x:c r="B460" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C460" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21577,7 +21577,7 @@
         <x:v>1986</x:v>
       </x:c>
       <x:c r="B461" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C461" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21624,7 +21624,7 @@
         <x:v>1947</x:v>
       </x:c>
       <x:c r="B462" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C462" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21669,7 +21669,7 @@
         <x:v>1466</x:v>
       </x:c>
       <x:c r="B463" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C463" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21716,7 +21716,7 @@
         <x:v>1400</x:v>
       </x:c>
       <x:c r="B464" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C464" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21761,7 +21761,7 @@
         <x:v>1972</x:v>
       </x:c>
       <x:c r="B465" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C465" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21808,7 +21808,7 @@
         <x:v>1543</x:v>
       </x:c>
       <x:c r="B466" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C466" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21853,7 +21853,7 @@
         <x:v>1504</x:v>
       </x:c>
       <x:c r="B467" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C467" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21896,7 +21896,7 @@
         <x:v>1094</x:v>
       </x:c>
       <x:c r="B468" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C468" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21945,7 +21945,7 @@
         <x:v>1938</x:v>
       </x:c>
       <x:c r="B469" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C469" s="14" t="str">
         <x:v>Core II</x:v>
@@ -21992,7 +21992,7 @@
         <x:v>1383</x:v>
       </x:c>
       <x:c r="B470" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C470" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22035,7 +22035,7 @@
         <x:v>1719</x:v>
       </x:c>
       <x:c r="B471" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C471" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22082,7 +22082,7 @@
         <x:v>1283</x:v>
       </x:c>
       <x:c r="B472" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C472" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22125,7 +22125,7 @@
         <x:v>1300</x:v>
       </x:c>
       <x:c r="B473" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C473" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22168,7 +22168,7 @@
         <x:v>1953</x:v>
       </x:c>
       <x:c r="B474" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C474" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22211,7 +22211,7 @@
         <x:v>1176</x:v>
       </x:c>
       <x:c r="B475" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C475" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22256,7 +22256,7 @@
         <x:v>1765</x:v>
       </x:c>
       <x:c r="B476" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C476" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22299,7 +22299,7 @@
         <x:v>1721</x:v>
       </x:c>
       <x:c r="B477" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C477" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22342,7 +22342,7 @@
         <x:v>2067</x:v>
       </x:c>
       <x:c r="B478" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C478" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22389,7 +22389,7 @@
         <x:v>1671</x:v>
       </x:c>
       <x:c r="B479" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C479" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22436,7 +22436,7 @@
         <x:v>1234</x:v>
       </x:c>
       <x:c r="B480" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C480" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22483,7 +22483,7 @@
         <x:v>1798</x:v>
       </x:c>
       <x:c r="B481" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C481" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22530,7 +22530,7 @@
         <x:v>1829</x:v>
       </x:c>
       <x:c r="B482" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C482" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22577,7 +22577,7 @@
         <x:v>2040</x:v>
       </x:c>
       <x:c r="B483" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C483" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22622,7 +22622,7 @@
         <x:v>1606</x:v>
       </x:c>
       <x:c r="B484" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C484" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22667,7 +22667,7 @@
         <x:v>1690</x:v>
       </x:c>
       <x:c r="B485" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C485" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22716,7 +22716,7 @@
         <x:v>1867</x:v>
       </x:c>
       <x:c r="B486" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C486" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22759,7 +22759,7 @@
         <x:v>1515</x:v>
       </x:c>
       <x:c r="B487" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C487" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22806,7 +22806,7 @@
         <x:v>1338</x:v>
       </x:c>
       <x:c r="B488" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C488" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22849,7 +22849,7 @@
         <x:v>1896</x:v>
       </x:c>
       <x:c r="B489" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C489" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22896,7 +22896,7 @@
         <x:v>1173</x:v>
       </x:c>
       <x:c r="B490" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C490" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22939,7 +22939,7 @@
         <x:v>1841</x:v>
       </x:c>
       <x:c r="B491" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C491" s="14" t="str">
         <x:v>Core II</x:v>
@@ -22982,7 +22982,7 @@
         <x:v>1855</x:v>
       </x:c>
       <x:c r="B492" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C492" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23031,7 +23031,7 @@
         <x:v>1128</x:v>
       </x:c>
       <x:c r="B493" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C493" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23074,7 +23074,7 @@
         <x:v>1194</x:v>
       </x:c>
       <x:c r="B494" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C494" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23119,7 +23119,7 @@
         <x:v>1976</x:v>
       </x:c>
       <x:c r="B495" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C495" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23164,7 +23164,7 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B496" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C496" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23211,7 +23211,7 @@
         <x:v>1945</x:v>
       </x:c>
       <x:c r="B497" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C497" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23260,7 +23260,7 @@
         <x:v>1673</x:v>
       </x:c>
       <x:c r="B498" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C498" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23307,7 +23307,7 @@
         <x:v>1985</x:v>
       </x:c>
       <x:c r="B499" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C499" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23360,7 +23360,7 @@
         <x:v>2135</x:v>
       </x:c>
       <x:c r="B500" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C500" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23405,7 +23405,7 @@
         <x:v>1845</x:v>
       </x:c>
       <x:c r="B501" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C501" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23452,7 +23452,7 @@
         <x:v>1331</x:v>
       </x:c>
       <x:c r="B502" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C502" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23499,7 +23499,7 @@
         <x:v>1963</x:v>
       </x:c>
       <x:c r="B503" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C503" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23542,7 +23542,7 @@
         <x:v>1296</x:v>
       </x:c>
       <x:c r="B504" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C504" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23589,7 +23589,7 @@
         <x:v>2124</x:v>
       </x:c>
       <x:c r="B505" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C505" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23634,7 +23634,7 @@
         <x:v>2070</x:v>
       </x:c>
       <x:c r="B506" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C506" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23679,7 +23679,7 @@
         <x:v>1691</x:v>
       </x:c>
       <x:c r="B507" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C507" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23726,7 +23726,7 @@
         <x:v>1783</x:v>
       </x:c>
       <x:c r="B508" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C508" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23773,7 +23773,7 @@
         <x:v>1978</x:v>
       </x:c>
       <x:c r="B509" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C509" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23816,7 +23816,7 @@
         <x:v>1451</x:v>
       </x:c>
       <x:c r="B510" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C510" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23863,7 +23863,7 @@
         <x:v>1708</x:v>
       </x:c>
       <x:c r="B511" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C511" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23906,7 +23906,7 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B512" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C512" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23949,7 +23949,7 @@
         <x:v>1284</x:v>
       </x:c>
       <x:c r="B513" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C513" s="14" t="str">
         <x:v>Core II</x:v>
@@ -23994,7 +23994,7 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B514" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C514" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24039,7 +24039,7 @@
         <x:v>1403</x:v>
       </x:c>
       <x:c r="B515" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C515" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24084,7 +24084,7 @@
         <x:v>1761</x:v>
       </x:c>
       <x:c r="B516" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C516" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24127,7 +24127,7 @@
         <x:v>1604</x:v>
       </x:c>
       <x:c r="B517" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C517" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24170,7 +24170,7 @@
         <x:v>2146</x:v>
       </x:c>
       <x:c r="B518" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C518" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24217,7 +24217,7 @@
         <x:v>1123</x:v>
       </x:c>
       <x:c r="B519" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C519" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24260,7 +24260,7 @@
         <x:v>2152</x:v>
       </x:c>
       <x:c r="B520" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C520" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24305,7 +24305,7 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B521" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C521" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24348,7 +24348,7 @@
         <x:v>1359</x:v>
       </x:c>
       <x:c r="B522" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C522" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24393,7 +24393,7 @@
         <x:v>2122</x:v>
       </x:c>
       <x:c r="B523" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C523" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24442,7 +24442,7 @@
         <x:v>1511</x:v>
       </x:c>
       <x:c r="B524" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C524" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24489,7 +24489,7 @@
         <x:v>1385</x:v>
       </x:c>
       <x:c r="B525" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C525" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24542,7 +24542,7 @@
         <x:v>1767</x:v>
       </x:c>
       <x:c r="B526" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C526" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24589,7 +24589,7 @@
         <x:v>1705</x:v>
       </x:c>
       <x:c r="B527" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C527" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24634,7 +24634,7 @@
         <x:v>1329</x:v>
       </x:c>
       <x:c r="B528" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C528" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24679,7 +24679,7 @@
         <x:v>1443</x:v>
       </x:c>
       <x:c r="B529" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C529" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24722,7 +24722,7 @@
         <x:v>2112</x:v>
       </x:c>
       <x:c r="B530" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C530" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24769,7 +24769,7 @@
         <x:v>1302</x:v>
       </x:c>
       <x:c r="B531" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C531" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24812,7 +24812,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B532" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C532" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24857,7 +24857,7 @@
         <x:v>1982</x:v>
       </x:c>
       <x:c r="B533" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C533" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24904,7 +24904,7 @@
         <x:v>1741</x:v>
       </x:c>
       <x:c r="B534" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C534" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24951,7 +24951,7 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B535" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C535" s="14" t="str">
         <x:v>Core II</x:v>
@@ -24996,7 +24996,7 @@
         <x:v>1811</x:v>
       </x:c>
       <x:c r="B536" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C536" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25041,7 +25041,7 @@
         <x:v>1837</x:v>
       </x:c>
       <x:c r="B537" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C537" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25090,7 +25090,7 @@
         <x:v>1289</x:v>
       </x:c>
       <x:c r="B538" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C538" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25133,7 +25133,7 @@
         <x:v>1633</x:v>
       </x:c>
       <x:c r="B539" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C539" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25176,7 +25176,7 @@
         <x:v>1104</x:v>
       </x:c>
       <x:c r="B540" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C540" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25229,7 +25229,7 @@
         <x:v>1463</x:v>
       </x:c>
       <x:c r="B541" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C541" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25278,7 +25278,7 @@
         <x:v>1602</x:v>
       </x:c>
       <x:c r="B542" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C542" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25333,7 +25333,7 @@
         <x:v>1489</x:v>
       </x:c>
       <x:c r="B543" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C543" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25378,7 +25378,7 @@
         <x:v>1461</x:v>
       </x:c>
       <x:c r="B544" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C544" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25423,7 +25423,7 @@
         <x:v>1357</x:v>
       </x:c>
       <x:c r="B545" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C545" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25468,7 +25468,7 @@
         <x:v>2131</x:v>
       </x:c>
       <x:c r="B546" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C546" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25515,7 +25515,7 @@
         <x:v>1150</x:v>
       </x:c>
       <x:c r="B547" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C547" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25562,7 +25562,7 @@
         <x:v>1275</x:v>
       </x:c>
       <x:c r="B548" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C548" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25607,7 +25607,7 @@
         <x:v>1160</x:v>
       </x:c>
       <x:c r="B549" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C549" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25652,7 +25652,7 @@
         <x:v>1303</x:v>
       </x:c>
       <x:c r="B550" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C550" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25695,7 +25695,7 @@
         <x:v>1347</x:v>
       </x:c>
       <x:c r="B551" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C551" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25738,7 +25738,7 @@
         <x:v>1977</x:v>
       </x:c>
       <x:c r="B552" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C552" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25781,7 +25781,7 @@
         <x:v>2052</x:v>
       </x:c>
       <x:c r="B553" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C553" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25824,7 +25824,7 @@
         <x:v>1251</x:v>
       </x:c>
       <x:c r="B554" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C554" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25869,7 +25869,7 @@
         <x:v>1139</x:v>
       </x:c>
       <x:c r="B555" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C555" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25918,7 +25918,7 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="B556" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C556" s="14" t="str">
         <x:v>Core II</x:v>
@@ -25961,7 +25961,7 @@
         <x:v>1171</x:v>
       </x:c>
       <x:c r="B557" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C557" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26010,7 +26010,7 @@
         <x:v>1394</x:v>
       </x:c>
       <x:c r="B558" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C558" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26055,7 +26055,7 @@
         <x:v>1108</x:v>
       </x:c>
       <x:c r="B559" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C559" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26100,7 +26100,7 @@
         <x:v>1428</x:v>
       </x:c>
       <x:c r="B560" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C560" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26147,7 +26147,7 @@
         <x:v>1609</x:v>
       </x:c>
       <x:c r="B561" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C561" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26192,7 +26192,7 @@
         <x:v>1485</x:v>
       </x:c>
       <x:c r="B562" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C562" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26235,7 +26235,7 @@
         <x:v>1968</x:v>
       </x:c>
       <x:c r="B563" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C563" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26280,7 +26280,7 @@
         <x:v>2017</x:v>
       </x:c>
       <x:c r="B564" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C564" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26329,7 +26329,7 @@
         <x:v>1790</x:v>
       </x:c>
       <x:c r="B565" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C565" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26376,7 +26376,7 @@
         <x:v>1227</x:v>
       </x:c>
       <x:c r="B566" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C566" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26425,7 +26425,7 @@
         <x:v>1168</x:v>
       </x:c>
       <x:c r="B567" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C567" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26470,7 +26470,7 @@
         <x:v>2155</x:v>
       </x:c>
       <x:c r="B568" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C568" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26517,7 +26517,7 @@
         <x:v>1784</x:v>
       </x:c>
       <x:c r="B569" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C569" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26564,7 +26564,7 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B570" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C570" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26609,7 +26609,7 @@
         <x:v>1551</x:v>
       </x:c>
       <x:c r="B571" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C571" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26654,7 +26654,7 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B572" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C572" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26699,7 +26699,7 @@
         <x:v>1853</x:v>
       </x:c>
       <x:c r="B573" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C573" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26744,7 +26744,7 @@
         <x:v>1730</x:v>
       </x:c>
       <x:c r="B574" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C574" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26789,7 +26789,7 @@
         <x:v>2125</x:v>
       </x:c>
       <x:c r="B575" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C575" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26834,7 +26834,7 @@
         <x:v>1470</x:v>
       </x:c>
       <x:c r="B576" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C576" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26877,7 +26877,7 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B577" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C577" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26924,7 +26924,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B578" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C578" s="14" t="str">
         <x:v>Core II</x:v>
@@ -26973,7 +26973,7 @@
         <x:v>1421</x:v>
       </x:c>
       <x:c r="B579" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C579" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27022,7 +27022,7 @@
         <x:v>2132</x:v>
       </x:c>
       <x:c r="B580" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C580" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27065,7 +27065,7 @@
         <x:v>1488</x:v>
       </x:c>
       <x:c r="B581" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C581" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27108,7 +27108,7 @@
         <x:v>1506</x:v>
       </x:c>
       <x:c r="B582" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C582" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27153,7 +27153,7 @@
         <x:v>2126</x:v>
       </x:c>
       <x:c r="B583" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C583" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27198,7 +27198,7 @@
         <x:v>2079</x:v>
       </x:c>
       <x:c r="B584" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C584" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27243,7 +27243,7 @@
         <x:v>1285</x:v>
       </x:c>
       <x:c r="B585" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C585" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27288,7 +27288,7 @@
         <x:v>1746</x:v>
       </x:c>
       <x:c r="B586" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C586" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27331,7 +27331,7 @@
         <x:v>1391</x:v>
       </x:c>
       <x:c r="B587" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C587" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27378,7 +27378,7 @@
         <x:v>1281</x:v>
       </x:c>
       <x:c r="B588" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C588" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27421,7 +27421,7 @@
         <x:v>1380</x:v>
       </x:c>
       <x:c r="B589" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C589" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27470,7 +27470,7 @@
         <x:v>1996</x:v>
       </x:c>
       <x:c r="B590" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C590" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27513,7 +27513,7 @@
         <x:v>1309</x:v>
       </x:c>
       <x:c r="B591" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C591" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27558,7 +27558,7 @@
         <x:v>1971</x:v>
       </x:c>
       <x:c r="B592" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C592" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27605,7 +27605,7 @@
         <x:v>1337</x:v>
       </x:c>
       <x:c r="B593" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C593" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27650,7 +27650,7 @@
         <x:v>1323</x:v>
       </x:c>
       <x:c r="B594" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C594" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27697,7 +27697,7 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B595" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C595" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27740,7 +27740,7 @@
         <x:v>1774</x:v>
       </x:c>
       <x:c r="B596" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C596" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27783,7 +27783,7 @@
         <x:v>1274</x:v>
       </x:c>
       <x:c r="B597" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C597" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27826,7 +27826,7 @@
         <x:v>1202</x:v>
       </x:c>
       <x:c r="B598" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C598" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27871,7 +27871,7 @@
         <x:v>1248</x:v>
       </x:c>
       <x:c r="B599" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C599" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27916,7 +27916,7 @@
         <x:v>1259</x:v>
       </x:c>
       <x:c r="B600" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C600" s="14" t="str">
         <x:v>Core II</x:v>
@@ -27963,7 +27963,7 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B601" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C601" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28006,7 +28006,7 @@
         <x:v>1144</x:v>
       </x:c>
       <x:c r="B602" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C602" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28051,7 +28051,7 @@
         <x:v>1838</x:v>
       </x:c>
       <x:c r="B603" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C603" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28094,7 +28094,7 @@
         <x:v>1967</x:v>
       </x:c>
       <x:c r="B604" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C604" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28137,7 +28137,7 @@
         <x:v>1998</x:v>
       </x:c>
       <x:c r="B605" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C605" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28182,7 +28182,7 @@
         <x:v>1799</x:v>
       </x:c>
       <x:c r="B606" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C606" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28227,7 +28227,7 @@
         <x:v>2060</x:v>
       </x:c>
       <x:c r="B607" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C607" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28270,7 +28270,7 @@
         <x:v>1808</x:v>
       </x:c>
       <x:c r="B608" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C608" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28317,7 +28317,7 @@
         <x:v>1228</x:v>
       </x:c>
       <x:c r="B609" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C609" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28360,7 +28360,7 @@
         <x:v>2028</x:v>
       </x:c>
       <x:c r="B610" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C610" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28403,7 +28403,7 @@
         <x:v>1464</x:v>
       </x:c>
       <x:c r="B611" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C611" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28446,7 +28446,7 @@
         <x:v>1935</x:v>
       </x:c>
       <x:c r="B612" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C612" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28489,7 +28489,7 @@
         <x:v>1397</x:v>
       </x:c>
       <x:c r="B613" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C613" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28532,7 +28532,7 @@
         <x:v>1225</x:v>
       </x:c>
       <x:c r="B614" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C614" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28575,7 +28575,7 @@
         <x:v>2119</x:v>
       </x:c>
       <x:c r="B615" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C615" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28618,7 +28618,7 @@
         <x:v>2138</x:v>
       </x:c>
       <x:c r="B616" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C616" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28661,7 +28661,7 @@
         <x:v>1381</x:v>
       </x:c>
       <x:c r="B617" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C617" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28704,7 +28704,7 @@
         <x:v>1802</x:v>
       </x:c>
       <x:c r="B618" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C618" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28753,7 +28753,7 @@
         <x:v>1368</x:v>
       </x:c>
       <x:c r="B619" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C619" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28796,7 +28796,7 @@
         <x:v>1873</x:v>
       </x:c>
       <x:c r="B620" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C620" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28843,7 +28843,7 @@
         <x:v>1438</x:v>
       </x:c>
       <x:c r="B621" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C621" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28888,7 +28888,7 @@
         <x:v>1439</x:v>
       </x:c>
       <x:c r="B622" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C622" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28933,7 +28933,7 @@
         <x:v>1449</x:v>
       </x:c>
       <x:c r="B623" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C623" s="14" t="str">
         <x:v>Core II</x:v>
@@ -28976,7 +28976,7 @@
         <x:v>1238</x:v>
       </x:c>
       <x:c r="B624" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C624" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29019,7 +29019,7 @@
         <x:v>1989</x:v>
       </x:c>
       <x:c r="B625" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C625" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29070,7 +29070,7 @@
         <x:v>2174</x:v>
       </x:c>
       <x:c r="B626" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C626" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29117,7 +29117,7 @@
         <x:v>1722</x:v>
       </x:c>
       <x:c r="B627" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C627" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29164,7 +29164,7 @@
         <x:v>2019</x:v>
       </x:c>
       <x:c r="B628" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C628" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29211,7 +29211,7 @@
         <x:v>1980</x:v>
       </x:c>
       <x:c r="B629" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C629" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29258,7 +29258,7 @@
         <x:v>1890</x:v>
       </x:c>
       <x:c r="B630" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C630" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29303,7 +29303,7 @@
         <x:v>1532</x:v>
       </x:c>
       <x:c r="B631" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C631" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29354,7 +29354,7 @@
         <x:v>1959</x:v>
       </x:c>
       <x:c r="B632" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C632" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29397,7 +29397,7 @@
         <x:v>1752</x:v>
       </x:c>
       <x:c r="B633" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C633" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29442,7 +29442,7 @@
         <x:v>2075</x:v>
       </x:c>
       <x:c r="B634" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C634" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29489,7 +29489,7 @@
         <x:v>1605</x:v>
       </x:c>
       <x:c r="B635" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C635" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29532,7 +29532,7 @@
         <x:v>2033</x:v>
       </x:c>
       <x:c r="B636" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C636" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29577,7 +29577,7 @@
         <x:v>1196</x:v>
       </x:c>
       <x:c r="B637" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C637" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29622,7 +29622,7 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B638" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C638" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29667,7 +29667,7 @@
         <x:v>1510</x:v>
       </x:c>
       <x:c r="B639" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C639" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29714,7 +29714,7 @@
         <x:v>1718</x:v>
       </x:c>
       <x:c r="B640" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C640" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29757,7 +29757,7 @@
         <x:v>1926</x:v>
       </x:c>
       <x:c r="B641" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C641" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29804,7 +29804,7 @@
         <x:v>1426</x:v>
       </x:c>
       <x:c r="B642" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C642" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29849,7 +29849,7 @@
         <x:v>1472</x:v>
       </x:c>
       <x:c r="B643" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C643" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29892,7 +29892,7 @@
         <x:v>1447</x:v>
       </x:c>
       <x:c r="B644" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C644" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29937,7 +29937,7 @@
         <x:v>1507</x:v>
       </x:c>
       <x:c r="B645" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C645" s="14" t="str">
         <x:v>Core II</x:v>
@@ -29982,7 +29982,7 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="B646" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C646" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30025,7 +30025,7 @@
         <x:v>1888</x:v>
       </x:c>
       <x:c r="B647" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C647" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30076,7 +30076,7 @@
         <x:v>1920</x:v>
       </x:c>
       <x:c r="B648" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C648" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30119,7 +30119,7 @@
         <x:v>1399</x:v>
       </x:c>
       <x:c r="B649" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C649" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30168,7 +30168,7 @@
         <x:v>2102</x:v>
       </x:c>
       <x:c r="B650" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C650" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30213,7 +30213,7 @@
         <x:v>1821</x:v>
       </x:c>
       <x:c r="B651" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C651" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30256,7 +30256,7 @@
         <x:v>2015</x:v>
       </x:c>
       <x:c r="B652" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C652" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30305,7 +30305,7 @@
         <x:v>1659</x:v>
       </x:c>
       <x:c r="B653" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C653" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30358,7 +30358,7 @@
         <x:v>1213</x:v>
       </x:c>
       <x:c r="B654" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C654" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30403,7 +30403,7 @@
         <x:v>1211</x:v>
       </x:c>
       <x:c r="B655" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C655" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30448,7 +30448,7 @@
         <x:v>1817</x:v>
       </x:c>
       <x:c r="B656" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C656" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30491,7 +30491,7 @@
         <x:v>1214</x:v>
       </x:c>
       <x:c r="B657" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C657" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30534,7 +30534,7 @@
         <x:v>1914</x:v>
       </x:c>
       <x:c r="B658" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C658" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30577,7 +30577,7 @@
         <x:v>1636</x:v>
       </x:c>
       <x:c r="B659" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C659" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30622,7 +30622,7 @@
         <x:v>1301</x:v>
       </x:c>
       <x:c r="B660" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C660" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30669,7 +30669,7 @@
         <x:v>1546</x:v>
       </x:c>
       <x:c r="B661" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C661" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30714,7 +30714,7 @@
         <x:v>1243</x:v>
       </x:c>
       <x:c r="B662" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C662" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30759,7 +30759,7 @@
         <x:v>1640</x:v>
       </x:c>
       <x:c r="B663" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C663" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30806,7 +30806,7 @@
         <x:v>1169</x:v>
       </x:c>
       <x:c r="B664" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C664" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30851,7 +30851,7 @@
         <x:v>1852</x:v>
       </x:c>
       <x:c r="B665" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C665" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30894,7 +30894,7 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B666" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C666" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30941,7 +30941,7 @@
         <x:v>2129</x:v>
       </x:c>
       <x:c r="B667" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C667" s="14" t="str">
         <x:v>Core II</x:v>
@@ -30998,7 +30998,7 @@
         <x:v>1363</x:v>
       </x:c>
       <x:c r="B668" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C668" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31041,7 +31041,7 @@
         <x:v>1099</x:v>
       </x:c>
       <x:c r="B669" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C669" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31084,7 +31084,7 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B670" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C670" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31129,7 +31129,7 @@
         <x:v>1635</x:v>
       </x:c>
       <x:c r="B671" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C671" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31174,7 +31174,7 @@
         <x:v>2153</x:v>
       </x:c>
       <x:c r="B672" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C672" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31219,7 +31219,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B673" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C673" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31264,7 +31264,7 @@
         <x:v>2093</x:v>
       </x:c>
       <x:c r="B674" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C674" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31307,7 +31307,7 @@
         <x:v>2100</x:v>
       </x:c>
       <x:c r="B675" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C675" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31360,7 +31360,7 @@
         <x:v>1267</x:v>
       </x:c>
       <x:c r="B676" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C676" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31405,7 +31405,7 @@
         <x:v>1373</x:v>
       </x:c>
       <x:c r="B677" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C677" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31448,7 +31448,7 @@
         <x:v>1559</x:v>
       </x:c>
       <x:c r="B678" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C678" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31495,7 +31495,7 @@
         <x:v>1854</x:v>
       </x:c>
       <x:c r="B679" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C679" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31540,7 +31540,7 @@
         <x:v>2042</x:v>
       </x:c>
       <x:c r="B680" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C680" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31583,7 +31583,7 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B681" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C681" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31636,7 +31636,7 @@
         <x:v>1187</x:v>
       </x:c>
       <x:c r="B682" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C682" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31679,7 +31679,7 @@
         <x:v>1437</x:v>
       </x:c>
       <x:c r="B683" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C683" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31726,7 +31726,7 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B684" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C684" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31771,7 +31771,7 @@
         <x:v>1132</x:v>
       </x:c>
       <x:c r="B685" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C685" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31820,7 +31820,7 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B686" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C686" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31863,7 +31863,7 @@
         <x:v>1193</x:v>
       </x:c>
       <x:c r="B687" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C687" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31908,7 +31908,7 @@
         <x:v>1819</x:v>
       </x:c>
       <x:c r="B688" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C688" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31951,7 +31951,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B689" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C689" s="14" t="str">
         <x:v>Core II</x:v>
@@ -31998,7 +31998,7 @@
         <x:v>1113</x:v>
       </x:c>
       <x:c r="B690" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C690" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32045,7 +32045,7 @@
         <x:v>1278</x:v>
       </x:c>
       <x:c r="B691" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C691" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32088,7 +32088,7 @@
         <x:v>1232</x:v>
       </x:c>
       <x:c r="B692" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C692" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32131,7 +32131,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="B693" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C693" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32178,7 +32178,7 @@
         <x:v>1939</x:v>
       </x:c>
       <x:c r="B694" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C694" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32223,7 +32223,7 @@
         <x:v>1782</x:v>
       </x:c>
       <x:c r="B695" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C695" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32266,7 +32266,7 @@
         <x:v>1188</x:v>
       </x:c>
       <x:c r="B696" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C696" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32309,7 +32309,7 @@
         <x:v>2127</x:v>
       </x:c>
       <x:c r="B697" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C697" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32356,7 +32356,7 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B698" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C698" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32401,7 +32401,7 @@
         <x:v>1256</x:v>
       </x:c>
       <x:c r="B699" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C699" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32448,7 +32448,7 @@
         <x:v>1831</x:v>
       </x:c>
       <x:c r="B700" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C700" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32493,7 +32493,7 @@
         <x:v>1268</x:v>
       </x:c>
       <x:c r="B701" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C701" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32542,7 +32542,7 @@
         <x:v>1556</x:v>
       </x:c>
       <x:c r="B702" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C702" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32591,7 +32591,7 @@
         <x:v>1563</x:v>
       </x:c>
       <x:c r="B703" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C703" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32634,7 +32634,7 @@
         <x:v>1503</x:v>
       </x:c>
       <x:c r="B704" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C704" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32681,7 +32681,7 @@
         <x:v>1223</x:v>
       </x:c>
       <x:c r="B705" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C705" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32728,7 +32728,7 @@
         <x:v>1930</x:v>
       </x:c>
       <x:c r="B706" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C706" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32771,7 +32771,7 @@
         <x:v>1734</x:v>
       </x:c>
       <x:c r="B707" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C707" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32814,7 +32814,7 @@
         <x:v>1272</x:v>
       </x:c>
       <x:c r="B708" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C708" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32857,7 +32857,7 @@
         <x:v>1452</x:v>
       </x:c>
       <x:c r="B709" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C709" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32900,7 +32900,7 @@
         <x:v>1620</x:v>
       </x:c>
       <x:c r="B710" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C710" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32947,7 +32947,7 @@
         <x:v>1785</x:v>
       </x:c>
       <x:c r="B711" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C711" s="14" t="str">
         <x:v>Core II</x:v>
@@ -32994,7 +32994,7 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B712" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C712" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33037,7 +33037,7 @@
         <x:v>1639</x:v>
       </x:c>
       <x:c r="B713" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C713" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33080,7 +33080,7 @@
         <x:v>1526</x:v>
       </x:c>
       <x:c r="B714" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C714" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33125,7 +33125,7 @@
         <x:v>1531</x:v>
       </x:c>
       <x:c r="B715" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C715" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33168,7 +33168,7 @@
         <x:v>1871</x:v>
       </x:c>
       <x:c r="B716" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C716" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33221,7 +33221,7 @@
         <x:v>1342</x:v>
       </x:c>
       <x:c r="B717" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C717" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33274,7 +33274,7 @@
         <x:v>1180</x:v>
       </x:c>
       <x:c r="B718" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C718" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33323,7 +33323,7 @@
         <x:v>1364</x:v>
       </x:c>
       <x:c r="B719" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C719" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33372,7 +33372,7 @@
         <x:v>1917</x:v>
       </x:c>
       <x:c r="B720" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C720" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33417,7 +33417,7 @@
         <x:v>1450</x:v>
       </x:c>
       <x:c r="B721" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C721" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33466,7 +33466,7 @@
         <x:v>1815</x:v>
       </x:c>
       <x:c r="B722" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C722" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33511,7 +33511,7 @@
         <x:v>1417</x:v>
       </x:c>
       <x:c r="B723" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C723" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33560,7 +33560,7 @@
         <x:v>1142</x:v>
       </x:c>
       <x:c r="B724" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C724" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33609,7 +33609,7 @@
         <x:v>1936</x:v>
       </x:c>
       <x:c r="B725" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C725" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33656,7 +33656,7 @@
         <x:v>1599</x:v>
       </x:c>
       <x:c r="B726" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C726" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33703,7 +33703,7 @@
         <x:v>1204</x:v>
       </x:c>
       <x:c r="B727" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C727" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33746,7 +33746,7 @@
         <x:v>2171</x:v>
       </x:c>
       <x:c r="B728" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C728" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33793,7 +33793,7 @@
         <x:v>1776</x:v>
       </x:c>
       <x:c r="B729" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C729" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33836,7 +33836,7 @@
         <x:v>1732</x:v>
       </x:c>
       <x:c r="B730" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C730" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33885,7 +33885,7 @@
         <x:v>1600</x:v>
       </x:c>
       <x:c r="B731" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C731" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33935,7 +33935,7 @@
         <x:v>1245</x:v>
       </x:c>
       <x:c r="B732" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C732" s="14" t="str">
         <x:v>Core II</x:v>
@@ -33984,7 +33984,7 @@
         <x:v>1803</x:v>
       </x:c>
       <x:c r="B733" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C733" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34031,7 +34031,7 @@
         <x:v>2145</x:v>
       </x:c>
       <x:c r="B734" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C734" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34074,7 +34074,7 @@
         <x:v>1582</x:v>
       </x:c>
       <x:c r="B735" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C735" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34119,7 +34119,7 @@
         <x:v>2072</x:v>
       </x:c>
       <x:c r="B736" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C736" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34164,7 +34164,7 @@
         <x:v>2094</x:v>
       </x:c>
       <x:c r="B737" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C737" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34207,7 +34207,7 @@
         <x:v>1514</x:v>
       </x:c>
       <x:c r="B738" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C738" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34254,7 +34254,7 @@
         <x:v>2068</x:v>
       </x:c>
       <x:c r="B739" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C739" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34299,7 +34299,7 @@
         <x:v>2095</x:v>
       </x:c>
       <x:c r="B740" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C740" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34348,7 +34348,7 @@
         <x:v>1172</x:v>
       </x:c>
       <x:c r="B741" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C741" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34391,7 +34391,7 @@
         <x:v>1473</x:v>
       </x:c>
       <x:c r="B742" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C742" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34436,7 +34436,7 @@
         <x:v>1549</x:v>
       </x:c>
       <x:c r="B743" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C743" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34479,7 +34479,7 @@
         <x:v>2098</x:v>
       </x:c>
       <x:c r="B744" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C744" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34528,7 +34528,7 @@
         <x:v>1796</x:v>
       </x:c>
       <x:c r="B745" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C745" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34571,7 +34571,7 @@
         <x:v>1979</x:v>
       </x:c>
       <x:c r="B746" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C746" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34614,7 +34614,7 @@
         <x:v>1668</x:v>
       </x:c>
       <x:c r="B747" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C747" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34657,7 +34657,7 @@
         <x:v>1365</x:v>
       </x:c>
       <x:c r="B748" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C748" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34708,7 +34708,7 @@
         <x:v>1455</x:v>
       </x:c>
       <x:c r="B749" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C749" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34755,7 +34755,7 @@
         <x:v>1894</x:v>
       </x:c>
       <x:c r="B750" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C750" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34802,7 +34802,7 @@
         <x:v>2134</x:v>
       </x:c>
       <x:c r="B751" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C751" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34851,7 +34851,7 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B752" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C752" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34898,7 +34898,7 @@
         <x:v>1493</x:v>
       </x:c>
       <x:c r="B753" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C753" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34941,7 +34941,7 @@
         <x:v>1786</x:v>
       </x:c>
       <x:c r="B754" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C754" s="14" t="str">
         <x:v>Core II</x:v>
@@ -34984,7 +34984,7 @@
         <x:v>1961</x:v>
       </x:c>
       <x:c r="B755" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C755" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35031,7 +35031,7 @@
         <x:v>1661</x:v>
       </x:c>
       <x:c r="B756" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C756" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35076,7 +35076,7 @@
         <x:v>1469</x:v>
       </x:c>
       <x:c r="B757" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C757" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35119,7 +35119,7 @@
         <x:v>2092</x:v>
       </x:c>
       <x:c r="B758" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C758" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35164,7 +35164,7 @@
         <x:v>1265</x:v>
       </x:c>
       <x:c r="B759" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C759" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35207,7 +35207,7 @@
         <x:v>1483</x:v>
       </x:c>
       <x:c r="B760" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C760" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35250,7 +35250,7 @@
         <x:v>1861</x:v>
       </x:c>
       <x:c r="B761" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C761" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35295,7 +35295,7 @@
         <x:v>2117</x:v>
       </x:c>
       <x:c r="B762" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C762" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35338,7 +35338,7 @@
         <x:v>1677</x:v>
       </x:c>
       <x:c r="B763" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C763" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35381,7 +35381,7 @@
         <x:v>1456</x:v>
       </x:c>
       <x:c r="B764" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C764" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35428,7 +35428,7 @@
         <x:v>1442</x:v>
       </x:c>
       <x:c r="B765" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C765" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35475,7 +35475,7 @@
         <x:v>2143</x:v>
       </x:c>
       <x:c r="B766" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C766" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35524,7 +35524,7 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B767" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C767" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35569,7 +35569,7 @@
         <x:v>1992</x:v>
       </x:c>
       <x:c r="B768" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C768" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35612,7 +35612,7 @@
         <x:v>1566</x:v>
       </x:c>
       <x:c r="B769" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C769" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35655,7 +35655,7 @@
         <x:v>1351</x:v>
       </x:c>
       <x:c r="B770" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C770" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35698,7 +35698,7 @@
         <x:v>1663</x:v>
       </x:c>
       <x:c r="B771" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C771" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35747,7 +35747,7 @@
         <x:v>1679</x:v>
       </x:c>
       <x:c r="B772" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C772" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35800,7 +35800,7 @@
         <x:v>1325</x:v>
       </x:c>
       <x:c r="B773" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C773" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35853,7 +35853,7 @@
         <x:v>1282</x:v>
       </x:c>
       <x:c r="B774" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C774" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35900,7 +35900,7 @@
         <x:v>1585</x:v>
       </x:c>
       <x:c r="B775" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C775" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35947,7 +35947,7 @@
         <x:v>1429</x:v>
       </x:c>
       <x:c r="B776" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C776" s="14" t="str">
         <x:v>Core II</x:v>
@@ -35990,7 +35990,7 @@
         <x:v>1121</x:v>
       </x:c>
       <x:c r="B777" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C777" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36039,7 +36039,7 @@
         <x:v>1588</x:v>
       </x:c>
       <x:c r="B778" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C778" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36084,7 +36084,7 @@
         <x:v>2022</x:v>
       </x:c>
       <x:c r="B779" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C779" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36127,7 +36127,7 @@
         <x:v>1596</x:v>
       </x:c>
       <x:c r="B780" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C780" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36174,7 +36174,7 @@
         <x:v>1943</x:v>
       </x:c>
       <x:c r="B781" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C781" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36229,7 +36229,7 @@
         <x:v>1631</x:v>
       </x:c>
       <x:c r="B782" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C782" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36272,7 +36272,7 @@
         <x:v>1994</x:v>
       </x:c>
       <x:c r="B783" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C783" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36317,7 +36317,7 @@
         <x:v>2111</x:v>
       </x:c>
       <x:c r="B784" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C784" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36366,7 +36366,7 @@
         <x:v>1457</x:v>
       </x:c>
       <x:c r="B785" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C785" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36411,7 +36411,7 @@
         <x:v>1902</x:v>
       </x:c>
       <x:c r="B786" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C786" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36454,7 +36454,7 @@
         <x:v>2045</x:v>
       </x:c>
       <x:c r="B787" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C787" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36499,7 +36499,7 @@
         <x:v>1496</x:v>
       </x:c>
       <x:c r="B788" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C788" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36542,7 +36542,7 @@
         <x:v>1436</x:v>
       </x:c>
       <x:c r="B789" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C789" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36591,7 +36591,7 @@
         <x:v>2168</x:v>
       </x:c>
       <x:c r="B790" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C790" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36642,7 +36642,7 @@
         <x:v>1941</x:v>
       </x:c>
       <x:c r="B791" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C791" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36687,7 +36687,7 @@
         <x:v>2163</x:v>
       </x:c>
       <x:c r="B792" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C792" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36732,7 +36732,7 @@
         <x:v>1413</x:v>
       </x:c>
       <x:c r="B793" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C793" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36779,7 +36779,7 @@
         <x:v>1990</x:v>
       </x:c>
       <x:c r="B794" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C794" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36822,7 +36822,7 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B795" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C795" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36867,7 +36867,7 @@
         <x:v>1432</x:v>
       </x:c>
       <x:c r="B796" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C796" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36914,7 +36914,7 @@
         <x:v>1929</x:v>
       </x:c>
       <x:c r="B797" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C797" s="14" t="str">
         <x:v>Core II</x:v>
@@ -36957,7 +36957,7 @@
         <x:v>1242</x:v>
       </x:c>
       <x:c r="B798" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C798" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37002,7 +37002,7 @@
         <x:v>1780</x:v>
       </x:c>
       <x:c r="B799" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C799" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37045,7 +37045,7 @@
         <x:v>1573</x:v>
       </x:c>
       <x:c r="B800" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C800" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37092,7 +37092,7 @@
         <x:v>1791</x:v>
       </x:c>
       <x:c r="B801" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C801" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37139,7 +37139,7 @@
         <x:v>2115</x:v>
       </x:c>
       <x:c r="B802" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C802" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37184,7 +37184,7 @@
         <x:v>1141</x:v>
       </x:c>
       <x:c r="B803" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C803" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37231,7 +37231,7 @@
         <x:v>1889</x:v>
       </x:c>
       <x:c r="B804" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C804" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37276,7 +37276,7 @@
         <x:v>2012</x:v>
       </x:c>
       <x:c r="B805" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C805" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37329,7 +37329,7 @@
         <x:v>1103</x:v>
       </x:c>
       <x:c r="B806" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C806" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37382,7 +37382,7 @@
         <x:v>1115</x:v>
       </x:c>
       <x:c r="B807" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C807" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37435,7 +37435,7 @@
         <x:v>1312</x:v>
       </x:c>
       <x:c r="B808" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C808" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37482,7 +37482,7 @@
         <x:v>1198</x:v>
       </x:c>
       <x:c r="B809" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C809" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37527,7 +37527,7 @@
         <x:v>1462</x:v>
       </x:c>
       <x:c r="B810" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C810" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37570,7 +37570,7 @@
         <x:v>1304</x:v>
       </x:c>
       <x:c r="B811" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C811" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37613,7 +37613,7 @@
         <x:v>1467</x:v>
       </x:c>
       <x:c r="B812" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C812" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37662,7 +37662,7 @@
         <x:v>2089</x:v>
       </x:c>
       <x:c r="B813" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C813" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37705,7 +37705,7 @@
         <x:v>2136</x:v>
       </x:c>
       <x:c r="B814" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C814" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37750,7 +37750,7 @@
         <x:v>1778</x:v>
       </x:c>
       <x:c r="B815" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C815" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37793,7 +37793,7 @@
         <x:v>1848</x:v>
       </x:c>
       <x:c r="B816" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C816" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37842,7 +37842,7 @@
         <x:v>1392</x:v>
       </x:c>
       <x:c r="B817" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C817" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37889,7 +37889,7 @@
         <x:v>1298</x:v>
       </x:c>
       <x:c r="B818" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C818" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37934,7 +37934,7 @@
         <x:v>2097</x:v>
       </x:c>
       <x:c r="B819" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C819" s="14" t="str">
         <x:v>Core II</x:v>
@@ -37981,7 +37981,7 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B820" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C820" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38030,7 +38030,7 @@
         <x:v>1645</x:v>
       </x:c>
       <x:c r="B821" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C821" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38073,7 +38073,7 @@
         <x:v>1916</x:v>
       </x:c>
       <x:c r="B822" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C822" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38122,7 +38122,7 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B823" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C823" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38165,7 +38165,7 @@
         <x:v>1384</x:v>
       </x:c>
       <x:c r="B824" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C824" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38208,7 +38208,7 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B825" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C825" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38257,7 +38257,7 @@
         <x:v>1572</x:v>
       </x:c>
       <x:c r="B826" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C826" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38300,7 +38300,7 @@
         <x:v>1124</x:v>
       </x:c>
       <x:c r="B827" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C827" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38343,7 +38343,7 @@
         <x:v>1792</x:v>
       </x:c>
       <x:c r="B828" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C828" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38388,7 +38388,7 @@
         <x:v>2023</x:v>
       </x:c>
       <x:c r="B829" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C829" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38435,7 +38435,7 @@
         <x:v>1898</x:v>
       </x:c>
       <x:c r="B830" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C830" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38482,7 +38482,7 @@
         <x:v>1131</x:v>
       </x:c>
       <x:c r="B831" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C831" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38531,7 +38531,7 @@
         <x:v>1330</x:v>
       </x:c>
       <x:c r="B832" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C832" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38576,7 +38576,7 @@
         <x:v>1110</x:v>
       </x:c>
       <x:c r="B833" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C833" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38623,7 +38623,7 @@
         <x:v>1571</x:v>
       </x:c>
       <x:c r="B834" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C834" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38666,7 +38666,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B835" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C835" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38715,7 +38715,7 @@
         <x:v>1949</x:v>
       </x:c>
       <x:c r="B836" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C836" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38758,7 +38758,7 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B837" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C837" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38807,7 +38807,7 @@
         <x:v>1269</x:v>
       </x:c>
       <x:c r="B838" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C838" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38854,7 +38854,7 @@
         <x:v>1235</x:v>
       </x:c>
       <x:c r="B839" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C839" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38901,7 +38901,7 @@
         <x:v>1814</x:v>
       </x:c>
       <x:c r="B840" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C840" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38948,7 +38948,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B841" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C841" s="14" t="str">
         <x:v>Core II</x:v>
@@ -38995,7 +38995,7 @@
         <x:v>1869</x:v>
       </x:c>
       <x:c r="B842" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C842" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39048,7 +39048,7 @@
         <x:v>1586</x:v>
       </x:c>
       <x:c r="B843" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C843" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39093,7 +39093,7 @@
         <x:v>1095</x:v>
       </x:c>
       <x:c r="B844" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C844" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39146,7 +39146,7 @@
         <x:v>1818</x:v>
       </x:c>
       <x:c r="B845" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C845" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39189,7 +39189,7 @@
         <x:v>1879</x:v>
       </x:c>
       <x:c r="B846" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C846" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39232,7 +39232,7 @@
         <x:v>2116</x:v>
       </x:c>
       <x:c r="B847" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C847" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39279,7 +39279,7 @@
         <x:v>1230</x:v>
       </x:c>
       <x:c r="B848" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C848" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39322,7 +39322,7 @@
         <x:v>1901</x:v>
       </x:c>
       <x:c r="B849" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C849" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39369,7 +39369,7 @@
         <x:v>1713</x:v>
       </x:c>
       <x:c r="B850" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C850" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39416,7 +39416,7 @@
         <x:v>1382</x:v>
       </x:c>
       <x:c r="B851" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C851" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39459,7 +39459,7 @@
         <x:v>1915</x:v>
       </x:c>
       <x:c r="B852" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C852" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39508,7 +39508,7 @@
         <x:v>1680</x:v>
       </x:c>
       <x:c r="B853" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C853" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39551,7 +39551,7 @@
         <x:v>2082</x:v>
       </x:c>
       <x:c r="B854" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C854" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39598,7 +39598,7 @@
         <x:v>1117</x:v>
       </x:c>
       <x:c r="B855" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C855" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39647,7 +39647,7 @@
         <x:v>1377</x:v>
       </x:c>
       <x:c r="B856" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C856" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39690,7 +39690,7 @@
         <x:v>1360</x:v>
       </x:c>
       <x:c r="B857" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C857" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39739,7 +39739,7 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B858" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C858" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39784,7 +39784,7 @@
         <x:v>1279</x:v>
       </x:c>
       <x:c r="B859" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C859" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39827,7 +39827,7 @@
         <x:v>2085</x:v>
       </x:c>
       <x:c r="B860" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C860" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39874,7 +39874,7 @@
         <x:v>1155</x:v>
       </x:c>
       <x:c r="B861" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C861" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39923,7 +39923,7 @@
         <x:v>1644</x:v>
       </x:c>
       <x:c r="B862" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C862" s="14" t="str">
         <x:v>Core II</x:v>
@@ -39966,7 +39966,7 @@
         <x:v>2025</x:v>
       </x:c>
       <x:c r="B863" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C863" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40013,7 +40013,7 @@
         <x:v>1630</x:v>
       </x:c>
       <x:c r="B864" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C864" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40056,7 +40056,7 @@
         <x:v>1477</x:v>
       </x:c>
       <x:c r="B865" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C865" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40099,7 +40099,7 @@
         <x:v>1518</x:v>
       </x:c>
       <x:c r="B866" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C866" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40144,7 +40144,7 @@
         <x:v>1724</x:v>
       </x:c>
       <x:c r="B867" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C867" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40191,7 +40191,7 @@
         <x:v>2031</x:v>
       </x:c>
       <x:c r="B868" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C868" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40234,7 +40234,7 @@
         <x:v>1354</x:v>
       </x:c>
       <x:c r="B869" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C869" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40283,7 +40283,7 @@
         <x:v>1528</x:v>
       </x:c>
       <x:c r="B870" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C870" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40328,7 +40328,7 @@
         <x:v>1130</x:v>
       </x:c>
       <x:c r="B871" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C871" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40377,7 +40377,7 @@
         <x:v>1378</x:v>
       </x:c>
       <x:c r="B872" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C872" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40426,7 +40426,7 @@
         <x:v>1222</x:v>
       </x:c>
       <x:c r="B873" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C873" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40469,7 +40469,7 @@
         <x:v>1944</x:v>
       </x:c>
       <x:c r="B874" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C874" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40512,7 +40512,7 @@
         <x:v>1839</x:v>
       </x:c>
       <x:c r="B875" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C875" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40563,7 +40563,7 @@
         <x:v>2133</x:v>
       </x:c>
       <x:c r="B876" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C876" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40616,7 +40616,7 @@
         <x:v>2144</x:v>
       </x:c>
       <x:c r="B877" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C877" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40661,7 +40661,7 @@
         <x:v>1326</x:v>
       </x:c>
       <x:c r="B878" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C878" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40704,7 +40704,7 @@
         <x:v>1151</x:v>
       </x:c>
       <x:c r="B879" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C879" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40751,7 +40751,7 @@
         <x:v>2066</x:v>
       </x:c>
       <x:c r="B880" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C880" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40798,7 +40798,7 @@
         <x:v>1241</x:v>
       </x:c>
       <x:c r="B881" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C881" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40845,7 +40845,7 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B882" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C882" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40898,7 +40898,7 @@
         <x:v>1863</x:v>
       </x:c>
       <x:c r="B883" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C883" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40945,7 +40945,7 @@
         <x:v>1593</x:v>
       </x:c>
       <x:c r="B884" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C884" s="14" t="str">
         <x:v>Core II</x:v>
@@ -40990,7 +40990,7 @@
         <x:v>1419</x:v>
       </x:c>
       <x:c r="B885" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C885" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41033,7 +41033,7 @@
         <x:v>1097</x:v>
       </x:c>
       <x:c r="B886" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C886" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41076,7 +41076,7 @@
         <x:v>1666</x:v>
       </x:c>
       <x:c r="B887" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C887" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41125,7 +41125,7 @@
         <x:v>1239</x:v>
       </x:c>
       <x:c r="B888" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C888" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41168,7 +41168,7 @@
         <x:v>1138</x:v>
       </x:c>
       <x:c r="B889" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C889" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41221,7 +41221,7 @@
         <x:v>2148</x:v>
       </x:c>
       <x:c r="B890" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C890" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41264,7 +41264,7 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B891" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C891" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41311,7 +41311,7 @@
         <x:v>1471</x:v>
       </x:c>
       <x:c r="B892" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C892" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41354,7 +41354,7 @@
         <x:v>1983</x:v>
       </x:c>
       <x:c r="B893" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C893" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41399,7 +41399,7 @@
         <x:v>1835</x:v>
       </x:c>
       <x:c r="B894" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C894" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41446,7 +41446,7 @@
         <x:v>2013</x:v>
       </x:c>
       <x:c r="B895" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C895" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41489,7 +41489,7 @@
         <x:v>1956</x:v>
       </x:c>
       <x:c r="B896" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C896" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41534,7 +41534,7 @@
         <x:v>1430</x:v>
       </x:c>
       <x:c r="B897" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C897" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41577,7 +41577,7 @@
         <x:v>1334</x:v>
       </x:c>
       <x:c r="B898" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C898" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41622,7 +41622,7 @@
         <x:v>2026</x:v>
       </x:c>
       <x:c r="B899" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C899" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41671,7 +41671,7 @@
         <x:v>2083</x:v>
       </x:c>
       <x:c r="B900" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C900" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41718,7 +41718,7 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B901" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C901" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41763,7 +41763,7 @@
         <x:v>2169</x:v>
       </x:c>
       <x:c r="B902" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C902" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41808,7 +41808,7 @@
         <x:v>1237</x:v>
       </x:c>
       <x:c r="B903" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C903" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41853,7 +41853,7 @@
         <x:v>1948</x:v>
       </x:c>
       <x:c r="B904" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C904" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41896,7 +41896,7 @@
         <x:v>1295</x:v>
       </x:c>
       <x:c r="B905" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C905" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41945,7 +41945,7 @@
         <x:v>1974</x:v>
       </x:c>
       <x:c r="B906" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C906" s="14" t="str">
         <x:v>Core II</x:v>
@@ -41992,7 +41992,7 @@
         <x:v>2088</x:v>
       </x:c>
       <x:c r="B907" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C907" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42035,7 +42035,7 @@
         <x:v>1353</x:v>
       </x:c>
       <x:c r="B908" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C908" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42078,7 +42078,7 @@
         <x:v>2161</x:v>
       </x:c>
       <x:c r="B909" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C909" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42123,7 +42123,7 @@
         <x:v>1723</x:v>
       </x:c>
       <x:c r="B910" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C910" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42170,7 +42170,7 @@
         <x:v>1773</x:v>
       </x:c>
       <x:c r="B911" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C911" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42215,7 +42215,7 @@
         <x:v>1498</x:v>
       </x:c>
       <x:c r="B912" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C912" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42262,7 +42262,7 @@
         <x:v>1513</x:v>
       </x:c>
       <x:c r="B913" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C913" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42315,7 +42315,7 @@
         <x:v>1832</x:v>
       </x:c>
       <x:c r="B914" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C914" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42360,7 +42360,7 @@
         <x:v>1189</x:v>
       </x:c>
       <x:c r="B915" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C915" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42403,7 +42403,7 @@
         <x:v>1273</x:v>
       </x:c>
       <x:c r="B916" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C916" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42448,7 +42448,7 @@
         <x:v>1607</x:v>
       </x:c>
       <x:c r="B917" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C917" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42491,7 +42491,7 @@
         <x:v>1481</x:v>
       </x:c>
       <x:c r="B918" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C918" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42544,7 +42544,7 @@
         <x:v>1509</x:v>
       </x:c>
       <x:c r="B919" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C919" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42591,7 +42591,7 @@
         <x:v>1581</x:v>
       </x:c>
       <x:c r="B920" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C920" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42636,7 +42636,7 @@
         <x:v>1550</x:v>
       </x:c>
       <x:c r="B921" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C921" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42683,7 +42683,7 @@
         <x:v>2032</x:v>
       </x:c>
       <x:c r="B922" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C922" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42726,7 +42726,7 @@
         <x:v>1433</x:v>
       </x:c>
       <x:c r="B923" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C923" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42771,7 +42771,7 @@
         <x:v>2110</x:v>
       </x:c>
       <x:c r="B924" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C924" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42818,7 +42818,7 @@
         <x:v>1185</x:v>
       </x:c>
       <x:c r="B925" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C925" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42863,7 +42863,7 @@
         <x:v>2007</x:v>
       </x:c>
       <x:c r="B926" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C926" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42910,7 +42910,7 @@
         <x:v>2016</x:v>
       </x:c>
       <x:c r="B927" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C927" s="14" t="str">
         <x:v>Core II</x:v>
@@ -42959,7 +42959,7 @@
         <x:v>1146</x:v>
       </x:c>
       <x:c r="B928" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C928" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43012,7 +43012,7 @@
         <x:v>1109</x:v>
       </x:c>
       <x:c r="B929" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C929" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43059,7 +43059,7 @@
         <x:v>1969</x:v>
       </x:c>
       <x:c r="B930" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C930" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43104,7 +43104,7 @@
         <x:v>1562</x:v>
       </x:c>
       <x:c r="B931" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C931" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43151,7 +43151,7 @@
         <x:v>2091</x:v>
       </x:c>
       <x:c r="B932" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C932" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43196,7 +43196,7 @@
         <x:v>1162</x:v>
       </x:c>
       <x:c r="B933" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C933" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43241,7 +43241,7 @@
         <x:v>1716</x:v>
       </x:c>
       <x:c r="B934" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C934" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43286,7 +43286,7 @@
         <x:v>1102</x:v>
       </x:c>
       <x:c r="B935" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C935" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43343,7 +43343,7 @@
         <x:v>1370</x:v>
       </x:c>
       <x:c r="B936" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C936" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43386,7 +43386,7 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B937" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C937" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43429,7 +43429,7 @@
         <x:v>1558</x:v>
       </x:c>
       <x:c r="B938" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C938" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43472,7 +43472,7 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B939" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C939" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43517,7 +43517,7 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B940" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C940" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43564,7 +43564,7 @@
         <x:v>1294</x:v>
       </x:c>
       <x:c r="B941" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C941" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43611,7 +43611,7 @@
         <x:v>1932</x:v>
       </x:c>
       <x:c r="B942" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C942" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43654,7 +43654,7 @@
         <x:v>1361</x:v>
       </x:c>
       <x:c r="B943" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C943" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43703,7 +43703,7 @@
         <x:v>1844</x:v>
       </x:c>
       <x:c r="B944" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C944" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43746,7 +43746,7 @@
         <x:v>1695</x:v>
       </x:c>
       <x:c r="B945" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C945" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43793,7 +43793,7 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B946" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C946" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43840,7 +43840,7 @@
         <x:v>1557</x:v>
       </x:c>
       <x:c r="B947" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C947" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43883,7 +43883,7 @@
         <x:v>1937</x:v>
       </x:c>
       <x:c r="B948" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C948" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43926,7 +43926,7 @@
         <x:v>1704</x:v>
       </x:c>
       <x:c r="B949" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C949" s="14" t="str">
         <x:v>Core II</x:v>
@@ -43969,7 +43969,7 @@
         <x:v>2113</x:v>
       </x:c>
       <x:c r="B950" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C950" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44014,7 +44014,7 @@
         <x:v>1657</x:v>
       </x:c>
       <x:c r="B951" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C951" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44057,7 +44057,7 @@
         <x:v>1490</x:v>
       </x:c>
       <x:c r="B952" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C952" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44102,7 +44102,7 @@
         <x:v>1622</x:v>
       </x:c>
       <x:c r="B953" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C953" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44145,7 +44145,7 @@
         <x:v>1828</x:v>
       </x:c>
       <x:c r="B954" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C954" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44190,7 +44190,7 @@
         <x:v>1390</x:v>
       </x:c>
       <x:c r="B955" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C955" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44233,7 +44233,7 @@
         <x:v>2047</x:v>
       </x:c>
       <x:c r="B956" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C956" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44278,7 +44278,7 @@
         <x:v>1702</x:v>
       </x:c>
       <x:c r="B957" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C957" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44323,7 +44323,7 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B958" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C958" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44368,7 +44368,7 @@
         <x:v>1910</x:v>
       </x:c>
       <x:c r="B959" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C959" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44415,7 +44415,7 @@
         <x:v>1319</x:v>
       </x:c>
       <x:c r="B960" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C960" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44458,7 +44458,7 @@
         <x:v>1505</x:v>
       </x:c>
       <x:c r="B961" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C961" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44501,7 +44501,7 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B962" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C962" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44544,7 +44544,7 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="B963" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C963" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44589,7 +44589,7 @@
         <x:v>1568</x:v>
       </x:c>
       <x:c r="B964" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C964" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44636,7 +44636,7 @@
         <x:v>1856</x:v>
       </x:c>
       <x:c r="B965" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C965" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44685,7 +44685,7 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B966" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C966" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44734,7 +44734,7 @@
         <x:v>2170</x:v>
       </x:c>
       <x:c r="B967" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C967" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44779,7 +44779,7 @@
         <x:v>1777</x:v>
       </x:c>
       <x:c r="B968" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C968" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44822,7 +44822,7 @@
         <x:v>1266</x:v>
       </x:c>
       <x:c r="B969" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C969" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44865,7 +44865,7 @@
         <x:v>1676</x:v>
       </x:c>
       <x:c r="B970" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C970" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44908,7 +44908,7 @@
         <x:v>2096</x:v>
       </x:c>
       <x:c r="B971" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C971" s="14" t="str">
         <x:v>Core II</x:v>
@@ -44959,7 +44959,7 @@
         <x:v>1555</x:v>
       </x:c>
       <x:c r="B972" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C972" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45006,7 +45006,7 @@
         <x:v>1345</x:v>
       </x:c>
       <x:c r="B973" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C973" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45055,7 +45055,7 @@
         <x:v>1254</x:v>
       </x:c>
       <x:c r="B974" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C974" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45104,7 +45104,7 @@
         <x:v>1226</x:v>
       </x:c>
       <x:c r="B975" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C975" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45151,7 +45151,7 @@
         <x:v>1618</x:v>
       </x:c>
       <x:c r="B976" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C976" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45204,7 +45204,7 @@
         <x:v>1789</x:v>
       </x:c>
       <x:c r="B977" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C977" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45249,7 +45249,7 @@
         <x:v>1561</x:v>
       </x:c>
       <x:c r="B978" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C978" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45296,7 +45296,7 @@
         <x:v>1314</x:v>
       </x:c>
       <x:c r="B979" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C979" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45339,7 +45339,7 @@
         <x:v>1292</x:v>
       </x:c>
       <x:c r="B980" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C980" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45386,7 +45386,7 @@
         <x:v>1806</x:v>
       </x:c>
       <x:c r="B981" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C981" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45433,7 +45433,7 @@
         <x:v>1215</x:v>
       </x:c>
       <x:c r="B982" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C982" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45478,7 +45478,7 @@
         <x:v>1601</x:v>
       </x:c>
       <x:c r="B983" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C983" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45527,7 +45527,7 @@
         <x:v>1933</x:v>
       </x:c>
       <x:c r="B984" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C984" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45576,7 +45576,7 @@
         <x:v>2139</x:v>
       </x:c>
       <x:c r="B985" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C985" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45625,7 +45625,7 @@
         <x:v>1367</x:v>
       </x:c>
       <x:c r="B986" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C986" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45668,7 +45668,7 @@
         <x:v>1911</x:v>
       </x:c>
       <x:c r="B987" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C987" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45713,7 +45713,7 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B988" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C988" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45756,7 +45756,7 @@
         <x:v>1291</x:v>
       </x:c>
       <x:c r="B989" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C989" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45803,7 +45803,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B990" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C990" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45852,7 +45852,7 @@
         <x:v>1964</x:v>
       </x:c>
       <x:c r="B991" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C991" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45897,7 +45897,7 @@
         <x:v>1591</x:v>
       </x:c>
       <x:c r="B992" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C992" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45942,7 +45942,7 @@
         <x:v>1987</x:v>
       </x:c>
       <x:c r="B993" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C993" s="14" t="str">
         <x:v>Core II</x:v>
@@ -45989,7 +45989,7 @@
         <x:v>1136</x:v>
       </x:c>
       <x:c r="B994" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C994" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46042,7 +46042,7 @@
         <x:v>2041</x:v>
       </x:c>
       <x:c r="B995" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C995" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46091,7 +46091,7 @@
         <x:v>1738</x:v>
       </x:c>
       <x:c r="B996" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C996" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46138,7 +46138,7 @@
         <x:v>1435</x:v>
       </x:c>
       <x:c r="B997" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C997" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46181,7 +46181,7 @@
         <x:v>1954</x:v>
       </x:c>
       <x:c r="B998" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C998" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46224,7 +46224,7 @@
         <x:v>1369</x:v>
       </x:c>
       <x:c r="B999" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C999" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46271,7 +46271,7 @@
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B1000" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1000" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46314,7 +46314,7 @@
         <x:v>1868</x:v>
       </x:c>
       <x:c r="B1001" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1001" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46357,7 +46357,7 @@
         <x:v>1201</x:v>
       </x:c>
       <x:c r="B1002" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1002" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46402,7 +46402,7 @@
         <x:v>1276</x:v>
       </x:c>
       <x:c r="B1003" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1003" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46445,7 +46445,7 @@
         <x:v>1355</x:v>
       </x:c>
       <x:c r="B1004" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1004" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46498,7 +46498,7 @@
         <x:v>1717</x:v>
       </x:c>
       <x:c r="B1005" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1005" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46541,7 +46541,7 @@
         <x:v>1859</x:v>
       </x:c>
       <x:c r="B1006" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1006" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46588,7 +46588,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1007" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1007" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46641,7 +46641,7 @@
         <x:v>2011</x:v>
       </x:c>
       <x:c r="B1008" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1008" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46684,7 +46684,7 @@
         <x:v>1675</x:v>
       </x:c>
       <x:c r="B1009" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1009" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46729,7 +46729,7 @@
         <x:v>2114</x:v>
       </x:c>
       <x:c r="B1010" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1010" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46774,7 +46774,7 @@
         <x:v>1106</x:v>
       </x:c>
       <x:c r="B1011" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1011" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46821,7 +46821,7 @@
         <x:v>1220</x:v>
       </x:c>
       <x:c r="B1012" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1012" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46866,7 +46866,7 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1013" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1013" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46909,7 +46909,7 @@
         <x:v>1942</x:v>
       </x:c>
       <x:c r="B1014" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1014" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46954,7 +46954,7 @@
         <x:v>1851</x:v>
       </x:c>
       <x:c r="B1015" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1015" s="14" t="str">
         <x:v>Core II</x:v>
@@ -46999,7 +46999,7 @@
         <x:v>1182</x:v>
       </x:c>
       <x:c r="B1016" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1016" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47048,7 +47048,7 @@
         <x:v>1870</x:v>
       </x:c>
       <x:c r="B1017" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1017" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47095,7 +47095,7 @@
         <x:v>1297</x:v>
       </x:c>
       <x:c r="B1018" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1018" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47142,7 +47142,7 @@
         <x:v>1190</x:v>
       </x:c>
       <x:c r="B1019" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1019" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47189,7 +47189,7 @@
         <x:v>1840</x:v>
       </x:c>
       <x:c r="B1020" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1020" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47238,7 +47238,7 @@
         <x:v>1714</x:v>
       </x:c>
       <x:c r="B1021" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1021" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47283,7 +47283,7 @@
         <x:v>1127</x:v>
       </x:c>
       <x:c r="B1022" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1022" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47332,7 +47332,7 @@
         <x:v>1991</x:v>
       </x:c>
       <x:c r="B1023" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1023" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47379,7 +47379,7 @@
         <x:v>2069</x:v>
       </x:c>
       <x:c r="B1024" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1024" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47424,7 +47424,7 @@
         <x:v>2030</x:v>
       </x:c>
       <x:c r="B1025" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1025" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47467,7 +47467,7 @@
         <x:v>1875</x:v>
       </x:c>
       <x:c r="B1026" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1026" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47516,7 +47516,7 @@
         <x:v>1626</x:v>
       </x:c>
       <x:c r="B1027" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1027" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47559,7 +47559,7 @@
         <x:v>1642</x:v>
       </x:c>
       <x:c r="B1028" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1028" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47604,7 +47604,7 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1029" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1029" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47649,7 +47649,7 @@
         <x:v>2141</x:v>
       </x:c>
       <x:c r="B1030" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1030" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47702,7 +47702,7 @@
         <x:v>1336</x:v>
       </x:c>
       <x:c r="B1031" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1031" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47747,7 +47747,7 @@
         <x:v>1318</x:v>
       </x:c>
       <x:c r="B1032" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1032" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47796,7 +47796,7 @@
         <x:v>1145</x:v>
       </x:c>
       <x:c r="B1033" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1033" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47843,7 +47843,7 @@
         <x:v>1619</x:v>
       </x:c>
       <x:c r="B1034" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1034" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47886,7 +47886,7 @@
         <x:v>2120</x:v>
       </x:c>
       <x:c r="B1035" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1035" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47933,7 +47933,7 @@
         <x:v>1527</x:v>
       </x:c>
       <x:c r="B1036" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1036" s="14" t="str">
         <x:v>Core II</x:v>
@@ -47978,7 +47978,7 @@
         <x:v>1541</x:v>
       </x:c>
       <x:c r="B1037" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1037" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48025,7 +48025,7 @@
         <x:v>1701</x:v>
       </x:c>
       <x:c r="B1038" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1038" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48070,7 +48070,7 @@
         <x:v>1834</x:v>
       </x:c>
       <x:c r="B1039" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1039" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48123,7 +48123,7 @@
         <x:v>1692</x:v>
       </x:c>
       <x:c r="B1040" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1040" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48166,7 +48166,7 @@
         <x:v>1825</x:v>
       </x:c>
       <x:c r="B1041" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1041" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48211,7 +48211,7 @@
         <x:v>1328</x:v>
       </x:c>
       <x:c r="B1042" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1042" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48254,7 +48254,7 @@
         <x:v>1647</x:v>
       </x:c>
       <x:c r="B1043" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1043" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48299,7 +48299,7 @@
         <x:v>1698</x:v>
       </x:c>
       <x:c r="B1044" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1044" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48348,7 +48348,7 @@
         <x:v>1905</x:v>
       </x:c>
       <x:c r="B1045" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1045" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48391,7 +48391,7 @@
         <x:v>1583</x:v>
       </x:c>
       <x:c r="B1046" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1046" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48436,7 +48436,7 @@
         <x:v>2051</x:v>
       </x:c>
       <x:c r="B1047" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1047" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48483,7 +48483,7 @@
         <x:v>1759</x:v>
       </x:c>
       <x:c r="B1048" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1048" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48530,7 +48530,7 @@
         <x:v>2064</x:v>
       </x:c>
       <x:c r="B1049" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1049" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48573,7 +48573,7 @@
         <x:v>1277</x:v>
       </x:c>
       <x:c r="B1050" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1050" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48620,7 +48620,7 @@
         <x:v>1372</x:v>
       </x:c>
       <x:c r="B1051" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1051" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48663,7 +48663,7 @@
         <x:v>1610</x:v>
       </x:c>
       <x:c r="B1052" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1052" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48706,7 +48706,7 @@
         <x:v>1112</x:v>
       </x:c>
       <x:c r="B1053" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1053" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48749,7 +48749,7 @@
         <x:v>1864</x:v>
       </x:c>
       <x:c r="B1054" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1054" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48792,7 +48792,7 @@
         <x:v>1465</x:v>
       </x:c>
       <x:c r="B1055" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1055" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48841,7 +48841,7 @@
         <x:v>1164</x:v>
       </x:c>
       <x:c r="B1056" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1056" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48884,7 +48884,7 @@
         <x:v>1565</x:v>
       </x:c>
       <x:c r="B1057" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1057" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48933,7 +48933,7 @@
         <x:v>1895</x:v>
       </x:c>
       <x:c r="B1058" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1058" s="14" t="str">
         <x:v>Core II</x:v>
@@ -48980,7 +48980,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="B1059" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1059" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49025,7 +49025,7 @@
         <x:v>1218</x:v>
       </x:c>
       <x:c r="B1060" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1060" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49076,7 +49076,7 @@
         <x:v>1327</x:v>
       </x:c>
       <x:c r="B1061" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1061" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49123,7 +49123,7 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1062" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1062" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49170,7 +49170,7 @@
         <x:v>2071</x:v>
       </x:c>
       <x:c r="B1063" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1063" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49215,7 +49215,7 @@
         <x:v>1479</x:v>
       </x:c>
       <x:c r="B1064" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1064" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49264,7 +49264,7 @@
         <x:v>1709</x:v>
       </x:c>
       <x:c r="B1065" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1065" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49311,7 +49311,7 @@
         <x:v>1616</x:v>
       </x:c>
       <x:c r="B1066" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1066" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49360,7 +49360,7 @@
         <x:v>1984</x:v>
       </x:c>
       <x:c r="B1067" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1067" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49405,7 +49405,7 @@
         <x:v>1195</x:v>
       </x:c>
       <x:c r="B1068" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1068" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49450,7 +49450,7 @@
         <x:v>2073</x:v>
       </x:c>
       <x:c r="B1069" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1069" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49495,7 +49495,7 @@
         <x:v>1569</x:v>
       </x:c>
       <x:c r="B1070" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1070" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49538,7 +49538,7 @@
         <x:v>1317</x:v>
       </x:c>
       <x:c r="B1071" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1071" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49585,7 +49585,7 @@
         <x:v>1246</x:v>
       </x:c>
       <x:c r="B1072" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1072" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49630,7 +49630,7 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1073" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1073" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49673,7 +49673,7 @@
         <x:v>1134</x:v>
       </x:c>
       <x:c r="B1074" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1074" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49716,7 +49716,7 @@
         <x:v>1603</x:v>
       </x:c>
       <x:c r="B1075" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1075" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49759,7 +49759,7 @@
         <x:v>1860</x:v>
       </x:c>
       <x:c r="B1076" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1076" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49804,7 +49804,7 @@
         <x:v>1174</x:v>
       </x:c>
       <x:c r="B1077" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1077" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49851,7 +49851,7 @@
         <x:v>1688</x:v>
       </x:c>
       <x:c r="B1078" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1078" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49896,7 +49896,7 @@
         <x:v>2056</x:v>
       </x:c>
       <x:c r="B1079" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1079" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49939,7 +49939,7 @@
         <x:v>2142</x:v>
       </x:c>
       <x:c r="B1080" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1080" s="14" t="str">
         <x:v>Core II</x:v>
@@ -49986,7 +49986,7 @@
         <x:v>1186</x:v>
       </x:c>
       <x:c r="B1081" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1081" s="14" t="str">
         <x:v>Core II</x:v>
@@ -50033,7 +50033,7 @@
         <x:v>1664</x:v>
       </x:c>
       <x:c r="B1082" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1082" s="14" t="str">
         <x:v>Core II</x:v>
@@ -50080,7 +50080,7 @@
         <x:v>1255</x:v>
       </x:c>
       <x:c r="B1083" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1083" s="14" t="str">
         <x:v>Core II</x:v>
@@ -50127,7 +50127,7 @@
         <x:v>1575</x:v>
       </x:c>
       <x:c r="B1084" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1084" s="14" t="str">
         <x:v>Core II</x:v>
@@ -50170,7 +50170,7 @@
         <x:v>1270</x:v>
       </x:c>
       <x:c r="B1085" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1085" s="14" t="str">
         <x:v>Core II</x:v>
@@ -50213,7 +50213,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1086" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1086" s="14" t="str">
         <x:v>Core II</x:v>
@@ -50258,7 +50258,7 @@
         <x:v>2103</x:v>
       </x:c>
       <x:c r="B1087" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1087" s="14" t="str">
         <x:v>Core II</x:v>
@@ -50305,7 +50305,7 @@
         <x:v>1850</x:v>
       </x:c>
       <x:c r="B1088" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1088" s="14" t="str">
         <x:v>Core II</x:v>
@@ -50350,7 +50350,7 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B1089" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1089" s="14" t="str">
         <x:v>Core II</x:v>
@@ -50395,7 +50395,7 @@
         <x:v>1170</x:v>
       </x:c>
       <x:c r="B1090" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1090" s="14" t="str">
         <x:v>Core II</x:v>
@@ -50452,7 +50452,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re15348261f004cba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dcba8449afb440c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -50617,10 +50617,10 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="43" t="str">
-        <x:v>Number of groups</x:v>
-      </x:c>
-      <x:c r="B13" s="44" t="n">
-        <x:v>20</x:v>
+        <x:v>Group number range</x:v>
+      </x:c>
+      <x:c r="B13" s="44" t="str">
+        <x:v>21–40</x:v>
       </x:c>
       <x:c r="C13" s="40"/>
       <x:c r="D13" s="40"/>
@@ -50632,7 +50632,7 @@
         <x:v>Smallest group</x:v>
       </x:c>
       <x:c r="B14" s="44" t="n">
-        <x:f>COUNTIF('Core II Data'!$B$5:$B$1090,20)</x:f>
+        <x:f>COUNTIF('Core II Data'!$B$5:$B$1090,40)</x:f>
         <x:v>54</x:v>
       </x:c>
       <x:c r="C14" s="40"/>
@@ -50645,7 +50645,7 @@
         <x:v>Largest group</x:v>
       </x:c>
       <x:c r="B15" s="46" t="n">
-        <x:f>COUNTIF('Core II Data'!$B$5:$B$1090,1)</x:f>
+        <x:f>COUNTIF('Core II Data'!$B$5:$B$1090,21)</x:f>
         <x:v>55</x:v>
       </x:c>
       <x:c r="C15" s="40"/>
@@ -50733,7 +50733,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="38" t="str">
-        <x:v>7. Records were randomly shuffled within Core II, then assigned sequentially to 20 near-equal groups. Shuffle seed: 144dc3776adf83833cb36b58d887de5deb59ebeab2a8cf95fffbdb609b1f2518</x:v>
+        <x:v>7. Records were randomly shuffled within Core II, then assigned sequentially to near-equal groups 21–40. Shuffle seed: 144dc3776adf83833cb36b58d887de5deb59ebeab2a8cf95fffbdb609b1f2518</x:v>
       </x:c>
       <x:c r="B24" s="38"/>
       <x:c r="C24" s="38"/>
